--- a/data/cox_xlsx/GABR.CO.xlsx
+++ b/data/cox_xlsx/GABR.CO.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="788" uniqueCount="400">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="788" uniqueCount="401">
   <si>
     <t>Company Fundamentals - Income Statement</t>
   </si>
@@ -760,6 +760,9 @@
   </si>
   <si>
     <t>Deferred Tax</t>
+  </si>
+  <si>
+    <t>Credit Institutions LT</t>
   </si>
   <si>
     <t>Total Non-current Liabilities</t>
@@ -1344,7 +1347,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="39">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1422,6 +1425,12 @@
     </xf>
     <xf borderId="3" fillId="0" fontId="7" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="0" fontId="3" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="3" fillId="0" fontId="8" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
@@ -11963,10 +11972,18 @@
       <c r="R84" s="20">
         <v>2.05</v>
       </c>
-      <c r="S84" s="18"/>
-      <c r="T84" s="18"/>
-      <c r="U84" s="18"/>
-      <c r="V84" s="18"/>
+      <c r="S84" s="26">
+        <v>0.0</v>
+      </c>
+      <c r="T84" s="26">
+        <v>0.0</v>
+      </c>
+      <c r="U84" s="26">
+        <v>0.0</v>
+      </c>
+      <c r="V84" s="26">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="85" ht="15.0" customHeight="1">
       <c r="A85" s="14" t="s">
@@ -12551,8 +12568,8 @@
       </c>
     </row>
     <row r="96" ht="15.0" customHeight="1">
-      <c r="A96" s="14" t="s">
-        <v>235</v>
+      <c r="A96" s="27" t="s">
+        <v>247</v>
       </c>
       <c r="B96" s="20">
         <v>48.72</v>
@@ -12674,7 +12691,7 @@
     </row>
     <row r="98" ht="15.0" customHeight="1">
       <c r="A98" s="16" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B98" s="17">
         <v>129.17</v>
@@ -12742,7 +12759,7 @@
     </row>
     <row r="99" ht="15.0" customHeight="1">
       <c r="A99" s="14" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B99" s="18"/>
       <c r="C99" s="18"/>
@@ -12776,7 +12793,7 @@
     </row>
     <row r="100" ht="15.0" customHeight="1">
       <c r="A100" s="16" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B100" s="17">
         <v>756.48</v>
@@ -12844,7 +12861,7 @@
     </row>
     <row r="101" ht="15.0" customHeight="1">
       <c r="A101" s="14" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B101" s="20">
         <v>59.32</v>
@@ -12912,7 +12929,7 @@
     </row>
     <row r="102" ht="15.0" customHeight="1">
       <c r="A102" s="14" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B102" s="19">
         <v>-25.31</v>
@@ -12980,7 +12997,7 @@
     </row>
     <row r="103" ht="15.0" customHeight="1">
       <c r="A103" s="14" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B103" s="18"/>
       <c r="C103" s="18"/>
@@ -13016,7 +13033,7 @@
     </row>
     <row r="104" ht="15.0" customHeight="1">
       <c r="A104" s="14" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B104" s="18"/>
       <c r="C104" s="18"/>
@@ -13054,7 +13071,7 @@
     </row>
     <row r="105" ht="15.0" customHeight="1">
       <c r="A105" s="14" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B105" s="15">
         <v>379.83</v>
@@ -13122,7 +13139,7 @@
     </row>
     <row r="106" ht="15.0" customHeight="1">
       <c r="A106" s="14" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B106" s="18">
         <v>0.0</v>
@@ -13190,7 +13207,7 @@
     </row>
     <row r="107" ht="15.0" customHeight="1">
       <c r="A107" s="14" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B107" s="18"/>
       <c r="C107" s="18"/>
@@ -13218,7 +13235,7 @@
     </row>
     <row r="108" ht="15.0" customHeight="1">
       <c r="A108" s="16" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B108" s="17">
         <v>413.85</v>
@@ -13286,7 +13303,7 @@
     </row>
     <row r="109" ht="15.0" customHeight="1">
       <c r="A109" s="14" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B109" s="18"/>
       <c r="C109" s="18"/>
@@ -13314,7 +13331,7 @@
     </row>
     <row r="110" ht="15.0" customHeight="1">
       <c r="A110" s="16" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B110" s="24"/>
       <c r="C110" s="24"/>
@@ -13342,7 +13359,7 @@
     </row>
     <row r="111" ht="15.0" customHeight="1">
       <c r="A111" s="16" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B111" s="17">
         <v>413.85</v>
@@ -13410,7 +13427,7 @@
     </row>
     <row r="112" ht="15.0" customHeight="1">
       <c r="A112" s="16" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B112" s="17">
         <v>1170.34</v>
@@ -13478,7 +13495,7 @@
     </row>
     <row r="113" ht="15.0" customHeight="1">
       <c r="A113" s="14" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B113" s="20">
         <v>1.89</v>
@@ -13546,7 +13563,7 @@
     </row>
     <row r="114" ht="15.0" customHeight="1">
       <c r="A114" s="14" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B114" s="18">
         <v>0.0</v>
@@ -13614,7 +13631,7 @@
     </row>
     <row r="115" ht="15.0" customHeight="1">
       <c r="A115" s="14" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B115" s="20">
         <v>1.89</v>
@@ -13682,7 +13699,7 @@
     </row>
     <row r="116" ht="15.0" customHeight="1">
       <c r="A116" s="14" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B116" s="20">
         <v>99.62</v>
@@ -13734,7 +13751,7 @@
     </row>
     <row r="117" ht="15.0" customHeight="1">
       <c r="A117" s="14" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B117" s="20">
         <v>51.83</v>
@@ -13786,7 +13803,7 @@
     </row>
     <row r="118" ht="15.0" customHeight="1">
       <c r="A118" s="14" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B118" s="20">
         <v>22.98</v>
@@ -13824,7 +13841,7 @@
     </row>
     <row r="119" ht="15.0" customHeight="1">
       <c r="A119" s="14" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B119" s="20">
         <v>24.82</v>
@@ -13876,7 +13893,7 @@
     </row>
     <row r="120" ht="15.0" customHeight="1">
       <c r="A120" s="14" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B120" s="20">
         <v>52.94</v>
@@ -13932,7 +13949,7 @@
     </row>
     <row r="121" ht="15.0" customHeight="1">
       <c r="A121" s="14" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B121" s="20">
         <v>4.22</v>
@@ -13988,7 +14005,7 @@
     </row>
     <row r="122" ht="15.0" customHeight="1">
       <c r="A122" s="14" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B122" s="20">
         <v>16.54</v>
@@ -14044,7 +14061,7 @@
     </row>
     <row r="123" ht="15.0" customHeight="1">
       <c r="A123" s="14" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B123" s="20">
         <v>32.18</v>
@@ -14100,7 +14117,7 @@
     </row>
     <row r="124" ht="15.0" customHeight="1">
       <c r="A124" s="14" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B124" s="20">
         <v>1.89</v>
@@ -14168,7 +14185,7 @@
     </row>
     <row r="125" ht="15.0" customHeight="1">
       <c r="A125" s="14" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B125" s="18">
         <v>0.0</v>
@@ -14236,7 +14253,7 @@
     </row>
     <row r="126" ht="15.0" customHeight="1">
       <c r="A126" s="14" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B126" s="20">
         <v>1.89</v>
@@ -14304,7 +14321,7 @@
     </row>
     <row r="127" ht="15.0" customHeight="1">
       <c r="A127" s="14" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B127" s="20">
         <v>1.0</v>
@@ -15264,7 +15281,7 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -15637,67 +15654,67 @@
         <v>43</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J15" s="10" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="K15" s="10" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="L15" s="10" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="M15" s="10" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="N15" s="10" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O15" s="10" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="P15" s="10" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q15" s="10" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="R15" s="10" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="S15" s="10" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="T15" s="10" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="U15" s="10" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="V15" s="10" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="16" ht="15.0" customHeight="1" outlineLevel="1">
@@ -15770,7 +15787,7 @@
     </row>
     <row r="18">
       <c r="A18" s="12" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -15864,7 +15881,7 @@
     </row>
     <row r="20" ht="15.0" customHeight="1">
       <c r="A20" s="14" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B20" s="19">
         <v>-27.23</v>
@@ -15894,7 +15911,7 @@
     </row>
     <row r="21" ht="15.0" customHeight="1">
       <c r="A21" s="14" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B21" s="20">
         <v>88.73</v>
@@ -15922,7 +15939,7 @@
     </row>
     <row r="22" ht="15.0" customHeight="1">
       <c r="A22" s="14" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B22" s="20">
         <v>19.86</v>
@@ -15960,7 +15977,7 @@
     </row>
     <row r="23" ht="15.0" customHeight="1">
       <c r="A23" s="14" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B23" s="15">
         <v>139.68</v>
@@ -15998,7 +16015,7 @@
     </row>
     <row r="24" ht="15.0" customHeight="1">
       <c r="A24" s="14" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B24" s="18"/>
       <c r="C24" s="18"/>
@@ -16038,7 +16055,7 @@
     </row>
     <row r="25" ht="15.0" customHeight="1">
       <c r="A25" s="14" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B25" s="20">
         <v>38.95</v>
@@ -16106,7 +16123,7 @@
     </row>
     <row r="26" ht="15.0" customHeight="1">
       <c r="A26" s="14" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B26" s="20">
         <v>0.73</v>
@@ -16150,7 +16167,7 @@
     </row>
     <row r="27" ht="15.0" customHeight="1">
       <c r="A27" s="14" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B27" s="18"/>
       <c r="C27" s="20">
@@ -16216,7 +16233,7 @@
     </row>
     <row r="28" ht="15.0" customHeight="1">
       <c r="A28" s="14" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B28" s="20">
         <v>6.02</v>
@@ -16266,7 +16283,7 @@
     </row>
     <row r="29" ht="15.0" customHeight="1">
       <c r="A29" s="14" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B29" s="18"/>
       <c r="C29" s="18"/>
@@ -16352,7 +16369,7 @@
     </row>
     <row r="31" ht="15.0" customHeight="1">
       <c r="A31" s="14" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B31" s="20">
         <v>17.03</v>
@@ -16392,7 +16409,7 @@
     </row>
     <row r="32" ht="15.0" customHeight="1">
       <c r="A32" s="14" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B32" s="20">
         <v>50.6</v>
@@ -16460,7 +16477,7 @@
     </row>
     <row r="33" ht="15.0" customHeight="1">
       <c r="A33" s="14" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B33" s="20">
         <v>35.92</v>
@@ -16528,7 +16545,7 @@
     </row>
     <row r="34" ht="15.0" customHeight="1">
       <c r="A34" s="14" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B34" s="19">
         <v>-13.14</v>
@@ -16596,7 +16613,7 @@
     </row>
     <row r="35" ht="15.0" customHeight="1">
       <c r="A35" s="14" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B35" s="19">
         <v>-18.69</v>
@@ -16648,7 +16665,7 @@
     </row>
     <row r="36" ht="15.0" customHeight="1">
       <c r="A36" s="14" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B36" s="20">
         <v>0.93</v>
@@ -16698,7 +16715,7 @@
     </row>
     <row r="37" ht="15.0" customHeight="1">
       <c r="A37" s="14" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B37" s="19">
         <v>-7.35</v>
@@ -16766,7 +16783,7 @@
     </row>
     <row r="38" ht="15.0" customHeight="1">
       <c r="A38" s="14" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B38" s="18"/>
       <c r="C38" s="18"/>
@@ -16796,7 +16813,7 @@
     </row>
     <row r="39" ht="15.0" customHeight="1">
       <c r="A39" s="14" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B39" s="18"/>
       <c r="C39" s="18"/>
@@ -16828,7 +16845,7 @@
     </row>
     <row r="40" ht="15.0" customHeight="1">
       <c r="A40" s="14" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B40" s="18"/>
       <c r="C40" s="18"/>
@@ -16856,7 +16873,7 @@
     </row>
     <row r="41" ht="15.0" customHeight="1">
       <c r="A41" s="16" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B41" s="17">
         <v>187.94</v>
@@ -16924,7 +16941,7 @@
     </row>
     <row r="42" ht="15.0" customHeight="1">
       <c r="A42" s="14" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B42" s="18"/>
       <c r="C42" s="18"/>
@@ -16966,7 +16983,7 @@
     </row>
     <row r="43" ht="15.0" customHeight="1">
       <c r="A43" s="14" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B43" s="19">
         <v>-13.16</v>
@@ -17034,7 +17051,7 @@
     </row>
     <row r="44" ht="15.0" customHeight="1">
       <c r="A44" s="14" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B44" s="19">
         <v>-14.01</v>
@@ -17102,7 +17119,7 @@
     </row>
     <row r="45" ht="15.0" customHeight="1">
       <c r="A45" s="14" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B45" s="18"/>
       <c r="C45" s="18"/>
@@ -17142,7 +17159,7 @@
     </row>
     <row r="46" ht="15.0" customHeight="1">
       <c r="A46" s="14" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B46" s="20">
         <v>3.85</v>
@@ -17204,7 +17221,7 @@
     </row>
     <row r="47" ht="15.0" customHeight="1">
       <c r="A47" s="14" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B47" s="18"/>
       <c r="C47" s="18"/>
@@ -17242,7 +17259,7 @@
     </row>
     <row r="48" ht="15.0" customHeight="1">
       <c r="A48" s="14" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B48" s="18"/>
       <c r="C48" s="18"/>
@@ -17282,7 +17299,7 @@
     </row>
     <row r="49" ht="15.0" customHeight="1">
       <c r="A49" s="14" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B49" s="18"/>
       <c r="C49" s="18"/>
@@ -17320,7 +17337,7 @@
     </row>
     <row r="50" ht="15.0" customHeight="1">
       <c r="A50" s="14" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B50" s="18"/>
       <c r="C50" s="18"/>
@@ -17350,7 +17367,7 @@
     </row>
     <row r="51" ht="15.0" customHeight="1">
       <c r="A51" s="14" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B51" s="18"/>
       <c r="C51" s="18"/>
@@ -17380,7 +17397,7 @@
     </row>
     <row r="52" ht="15.0" customHeight="1">
       <c r="A52" s="16" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B52" s="23">
         <v>-23.32</v>
@@ -17400,7 +17417,7 @@
       <c r="G52" s="23">
         <v>-43.14</v>
       </c>
-      <c r="H52" s="26">
+      <c r="H52" s="28">
         <v>-104.69</v>
       </c>
       <c r="I52" s="23">
@@ -17448,7 +17465,7 @@
     </row>
     <row r="53" ht="15.0" customHeight="1">
       <c r="A53" s="14" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B53" s="19">
         <v>-43.66</v>
@@ -17514,7 +17531,7 @@
     </row>
     <row r="54" ht="15.0" customHeight="1">
       <c r="A54" s="14" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B54" s="18"/>
       <c r="C54" s="20">
@@ -17542,7 +17559,7 @@
     </row>
     <row r="55" ht="15.0" customHeight="1">
       <c r="A55" s="14" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B55" s="19">
         <v>-80.06</v>
@@ -17570,7 +17587,7 @@
     </row>
     <row r="56" ht="15.0" customHeight="1">
       <c r="A56" s="14" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B56" s="18"/>
       <c r="C56" s="18"/>
@@ -17614,7 +17631,7 @@
     </row>
     <row r="57" ht="15.0" customHeight="1">
       <c r="A57" s="14" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B57" s="18"/>
       <c r="C57" s="18"/>
@@ -17654,7 +17671,7 @@
     </row>
     <row r="58" ht="15.0" customHeight="1">
       <c r="A58" s="14" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B58" s="18">
         <v>0.0</v>
@@ -17720,7 +17737,7 @@
     </row>
     <row r="59" ht="15.0" customHeight="1">
       <c r="A59" s="14" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B59" s="18"/>
       <c r="C59" s="18"/>
@@ -17748,7 +17765,7 @@
     </row>
     <row r="60" ht="15.0" customHeight="1">
       <c r="A60" s="14" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B60" s="18"/>
       <c r="C60" s="18"/>
@@ -17782,7 +17799,7 @@
     </row>
     <row r="61" ht="15.0" customHeight="1">
       <c r="A61" s="14" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B61" s="18"/>
       <c r="C61" s="18"/>
@@ -17822,7 +17839,7 @@
     </row>
     <row r="62" ht="15.0" customHeight="1">
       <c r="A62" s="14" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B62" s="18"/>
       <c r="C62" s="18"/>
@@ -17858,7 +17875,7 @@
     </row>
     <row r="63" ht="15.0" customHeight="1">
       <c r="A63" s="14" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B63" s="18"/>
       <c r="C63" s="18"/>
@@ -17890,7 +17907,7 @@
     </row>
     <row r="64" ht="15.0" customHeight="1">
       <c r="A64" s="14" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B64" s="18"/>
       <c r="C64" s="18"/>
@@ -17920,7 +17937,7 @@
     </row>
     <row r="65" ht="15.0" customHeight="1">
       <c r="A65" s="14" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B65" s="18"/>
       <c r="C65" s="18"/>
@@ -17948,9 +17965,9 @@
     </row>
     <row r="66" ht="15.0" customHeight="1">
       <c r="A66" s="16" t="s">
-        <v>324</v>
-      </c>
-      <c r="B66" s="26">
+        <v>325</v>
+      </c>
+      <c r="B66" s="28">
         <v>-123.72</v>
       </c>
       <c r="C66" s="23">
@@ -18016,7 +18033,7 @@
     </row>
     <row r="67" ht="15.0" customHeight="1">
       <c r="A67" s="14" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B67" s="18"/>
       <c r="C67" s="18"/>
@@ -18050,7 +18067,7 @@
     </row>
     <row r="68" ht="15.0" customHeight="1">
       <c r="A68" s="16" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B68" s="24"/>
       <c r="C68" s="24"/>
@@ -18084,7 +18101,7 @@
     </row>
     <row r="69" ht="15.0" customHeight="1">
       <c r="A69" s="14" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B69" s="18"/>
       <c r="C69" s="18"/>
@@ -18120,7 +18137,7 @@
     </row>
     <row r="70" ht="15.0" customHeight="1">
       <c r="A70" s="16" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B70" s="24"/>
       <c r="C70" s="24"/>
@@ -18156,7 +18173,7 @@
     </row>
     <row r="71" ht="15.0" customHeight="1">
       <c r="A71" s="14" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B71" s="20">
         <v>60.37</v>
@@ -18224,7 +18241,7 @@
     </row>
     <row r="72" ht="15.0" customHeight="1">
       <c r="A72" s="14" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B72" s="20">
         <v>99.77</v>
@@ -18292,7 +18309,7 @@
     </row>
     <row r="73" ht="15.0" customHeight="1">
       <c r="A73" s="14" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B73" s="19">
         <v>-1.5</v>
@@ -18342,7 +18359,7 @@
     </row>
     <row r="74" ht="15.0" customHeight="1">
       <c r="A74" s="14" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B74" s="18"/>
       <c r="C74" s="18"/>
@@ -18386,7 +18403,7 @@
     </row>
     <row r="75" ht="15.0" customHeight="1">
       <c r="A75" s="16" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B75" s="22">
         <v>39.4</v>
@@ -18397,7 +18414,7 @@
       <c r="D75" s="23">
         <v>-81.93</v>
       </c>
-      <c r="E75" s="26">
+      <c r="E75" s="28">
         <v>-100.63</v>
       </c>
       <c r="F75" s="23">
@@ -19398,7 +19415,7 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -19569,25 +19586,25 @@
         <v>38</v>
       </c>
       <c r="W11" s="7" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="X11" s="7" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Y11" s="7" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Z11" s="7" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AA11" s="7" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AB11" s="7" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AC11" s="7" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="12" ht="15.0" customHeight="1" outlineLevel="1">
@@ -20037,7 +20054,7 @@
     </row>
     <row r="18">
       <c r="A18" s="12" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -20136,3569 +20153,3569 @@
         <v>68</v>
       </c>
       <c r="W19" s="13" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="X19" s="13" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Y19" s="13" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Z19" s="13" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AA19" s="13" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AB19" s="13" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AC19" s="13" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="20" ht="15.0" customHeight="1">
-      <c r="A20" s="27" t="s">
-        <v>349</v>
-      </c>
-      <c r="B20" s="28"/>
-      <c r="C20" s="28"/>
-      <c r="D20" s="28"/>
-      <c r="E20" s="28"/>
-      <c r="F20" s="28"/>
-      <c r="G20" s="28"/>
-      <c r="H20" s="28"/>
-      <c r="I20" s="28"/>
-      <c r="J20" s="28"/>
-      <c r="K20" s="28"/>
-      <c r="L20" s="28"/>
-      <c r="M20" s="28"/>
-      <c r="N20" s="28"/>
-      <c r="O20" s="28"/>
-      <c r="P20" s="28"/>
-      <c r="Q20" s="28"/>
-      <c r="R20" s="28"/>
-      <c r="S20" s="28"/>
-      <c r="T20" s="28"/>
-      <c r="U20" s="28"/>
-      <c r="V20" s="28"/>
-      <c r="W20" s="28"/>
-      <c r="X20" s="28"/>
-      <c r="Y20" s="28"/>
-      <c r="Z20" s="28"/>
-      <c r="AA20" s="28"/>
-      <c r="AB20" s="28"/>
-      <c r="AC20" s="28"/>
+      <c r="A20" s="29" t="s">
+        <v>350</v>
+      </c>
+      <c r="B20" s="30"/>
+      <c r="C20" s="30"/>
+      <c r="D20" s="30"/>
+      <c r="E20" s="30"/>
+      <c r="F20" s="30"/>
+      <c r="G20" s="30"/>
+      <c r="H20" s="30"/>
+      <c r="I20" s="30"/>
+      <c r="J20" s="30"/>
+      <c r="K20" s="30"/>
+      <c r="L20" s="30"/>
+      <c r="M20" s="30"/>
+      <c r="N20" s="30"/>
+      <c r="O20" s="30"/>
+      <c r="P20" s="30"/>
+      <c r="Q20" s="30"/>
+      <c r="R20" s="30"/>
+      <c r="S20" s="30"/>
+      <c r="T20" s="30"/>
+      <c r="U20" s="30"/>
+      <c r="V20" s="30"/>
+      <c r="W20" s="30"/>
+      <c r="X20" s="30"/>
+      <c r="Y20" s="30"/>
+      <c r="Z20" s="30"/>
+      <c r="AA20" s="30"/>
+      <c r="AB20" s="30"/>
+      <c r="AC20" s="30"/>
     </row>
     <row r="21" ht="15.0" customHeight="1">
-      <c r="A21" s="29" t="s">
-        <v>349</v>
-      </c>
-      <c r="B21" s="30">
+      <c r="A21" s="31" t="s">
+        <v>350</v>
+      </c>
+      <c r="B21" s="32">
         <v>1213.45</v>
       </c>
-      <c r="C21" s="30">
+      <c r="C21" s="32">
         <v>1379.97</v>
       </c>
-      <c r="D21" s="30">
+      <c r="D21" s="32">
         <v>1423.75</v>
       </c>
-      <c r="E21" s="30">
+      <c r="E21" s="32">
         <v>1839.9</v>
       </c>
-      <c r="F21" s="30">
+      <c r="F21" s="32">
         <v>1954.31</v>
       </c>
-      <c r="G21" s="30">
+      <c r="G21" s="32">
         <v>2235.55</v>
       </c>
-      <c r="H21" s="30">
+      <c r="H21" s="32">
         <v>1969.79</v>
       </c>
-      <c r="I21" s="30">
+      <c r="I21" s="32">
         <v>1527.35</v>
       </c>
-      <c r="J21" s="30">
+      <c r="J21" s="32">
         <v>1187.33</v>
       </c>
-      <c r="K21" s="30">
+      <c r="K21" s="32">
         <v>1289.55</v>
       </c>
-      <c r="L21" s="30">
+      <c r="L21" s="32">
         <v>522.32</v>
       </c>
-      <c r="M21" s="30">
+      <c r="M21" s="32">
         <v>395.24</v>
       </c>
-      <c r="N21" s="30">
+      <c r="N21" s="32">
         <v>303.41</v>
       </c>
-      <c r="O21" s="30">
+      <c r="O21" s="32">
         <v>208.15</v>
       </c>
-      <c r="P21" s="30">
+      <c r="P21" s="32">
         <v>212.87</v>
       </c>
-      <c r="Q21" s="30">
+      <c r="Q21" s="32">
         <v>210.96</v>
       </c>
-      <c r="R21" s="30">
+      <c r="R21" s="32">
         <v>208.26</v>
       </c>
-      <c r="S21" s="30">
+      <c r="S21" s="32">
         <v>274.6</v>
       </c>
-      <c r="T21" s="30">
+      <c r="T21" s="32">
         <v>373.5</v>
       </c>
-      <c r="U21" s="30">
+      <c r="U21" s="32">
         <v>334.93</v>
       </c>
-      <c r="V21" s="30">
+      <c r="V21" s="32">
         <v>206.3</v>
       </c>
-      <c r="W21" s="30">
+      <c r="W21" s="32">
         <v>121.9</v>
       </c>
-      <c r="X21" s="31">
+      <c r="X21" s="33">
         <v>76.88</v>
       </c>
-      <c r="Y21" s="31">
+      <c r="Y21" s="33">
         <v>87.16</v>
       </c>
-      <c r="Z21" s="30">
+      <c r="Z21" s="32">
         <v>123.79</v>
       </c>
-      <c r="AA21" s="31">
+      <c r="AA21" s="33">
         <v>70.49</v>
       </c>
-      <c r="AB21" s="31">
+      <c r="AB21" s="33">
         <v>66.08</v>
       </c>
-      <c r="AC21" s="30">
+      <c r="AC21" s="32">
         <v>102.41</v>
       </c>
     </row>
     <row r="22" ht="15.0" customHeight="1">
-      <c r="A22" s="29" t="s">
-        <v>350</v>
-      </c>
-      <c r="B22" s="30">
+      <c r="A22" s="31" t="s">
+        <v>351</v>
+      </c>
+      <c r="B22" s="32">
         <v>1665.67</v>
       </c>
-      <c r="C22" s="30">
+      <c r="C22" s="32">
         <v>1907.52</v>
       </c>
-      <c r="D22" s="30">
+      <c r="D22" s="32">
         <v>2018.69</v>
       </c>
-      <c r="E22" s="30">
+      <c r="E22" s="32">
         <v>1988.21</v>
       </c>
-      <c r="F22" s="30">
+      <c r="F22" s="32">
         <v>1793.38</v>
       </c>
-      <c r="G22" s="30">
+      <c r="G22" s="32">
         <v>1827.42</v>
       </c>
-      <c r="H22" s="30">
+      <c r="H22" s="32">
         <v>1356.19</v>
       </c>
-      <c r="I22" s="30">
+      <c r="I22" s="32">
         <v>1010.49</v>
       </c>
-      <c r="J22" s="30">
+      <c r="J22" s="32">
         <v>773.3</v>
       </c>
-      <c r="K22" s="30">
+      <c r="K22" s="32">
         <v>562.01</v>
       </c>
-      <c r="L22" s="30">
+      <c r="L22" s="32">
         <v>373.19</v>
       </c>
-      <c r="M22" s="30">
+      <c r="M22" s="32">
         <v>272.47</v>
       </c>
-      <c r="N22" s="30">
+      <c r="N22" s="32">
         <v>233.55</v>
       </c>
-      <c r="O22" s="30">
+      <c r="O22" s="32">
         <v>205.37</v>
       </c>
-      <c r="P22" s="30">
+      <c r="P22" s="32">
         <v>251.54</v>
       </c>
-      <c r="Q22" s="30">
+      <c r="Q22" s="32">
         <v>277.31</v>
       </c>
-      <c r="R22" s="30">
+      <c r="R22" s="32">
         <v>292.85</v>
       </c>
-      <c r="S22" s="30">
+      <c r="S22" s="32">
         <v>269.48</v>
       </c>
-      <c r="T22" s="30">
+      <c r="T22" s="32">
         <v>213.99</v>
       </c>
-      <c r="U22" s="30">
+      <c r="U22" s="32">
         <v>169.88</v>
       </c>
-      <c r="V22" s="30">
+      <c r="V22" s="32">
         <v>121.62</v>
       </c>
-      <c r="W22" s="31">
+      <c r="W22" s="33">
         <v>99.92</v>
       </c>
-      <c r="X22" s="31">
+      <c r="X22" s="33">
         <v>87.99</v>
       </c>
-      <c r="Y22" s="31">
+      <c r="Y22" s="33">
         <v>81.85</v>
       </c>
-      <c r="Z22" s="32"/>
-      <c r="AA22" s="32"/>
-      <c r="AB22" s="32"/>
-      <c r="AC22" s="32"/>
+      <c r="Z22" s="34"/>
+      <c r="AA22" s="34"/>
+      <c r="AB22" s="34"/>
+      <c r="AC22" s="34"/>
     </row>
     <row r="23" ht="15.0" customHeight="1">
-      <c r="A23" s="27" t="s">
-        <v>351</v>
-      </c>
-      <c r="B23" s="28"/>
-      <c r="C23" s="28"/>
-      <c r="D23" s="28"/>
-      <c r="E23" s="28"/>
-      <c r="F23" s="28"/>
-      <c r="G23" s="28"/>
-      <c r="H23" s="28"/>
-      <c r="I23" s="28"/>
-      <c r="J23" s="28"/>
-      <c r="K23" s="28"/>
-      <c r="L23" s="28"/>
-      <c r="M23" s="28"/>
-      <c r="N23" s="28"/>
-      <c r="O23" s="28"/>
-      <c r="P23" s="28"/>
-      <c r="Q23" s="28"/>
-      <c r="R23" s="28"/>
-      <c r="S23" s="28"/>
-      <c r="T23" s="28"/>
-      <c r="U23" s="28"/>
-      <c r="V23" s="28"/>
-      <c r="W23" s="28"/>
-      <c r="X23" s="28"/>
-      <c r="Y23" s="28"/>
-      <c r="Z23" s="28"/>
-      <c r="AA23" s="28"/>
-      <c r="AB23" s="28"/>
-      <c r="AC23" s="28"/>
+      <c r="A23" s="29" t="s">
+        <v>352</v>
+      </c>
+      <c r="B23" s="30"/>
+      <c r="C23" s="30"/>
+      <c r="D23" s="30"/>
+      <c r="E23" s="30"/>
+      <c r="F23" s="30"/>
+      <c r="G23" s="30"/>
+      <c r="H23" s="30"/>
+      <c r="I23" s="30"/>
+      <c r="J23" s="30"/>
+      <c r="K23" s="30"/>
+      <c r="L23" s="30"/>
+      <c r="M23" s="30"/>
+      <c r="N23" s="30"/>
+      <c r="O23" s="30"/>
+      <c r="P23" s="30"/>
+      <c r="Q23" s="30"/>
+      <c r="R23" s="30"/>
+      <c r="S23" s="30"/>
+      <c r="T23" s="30"/>
+      <c r="U23" s="30"/>
+      <c r="V23" s="30"/>
+      <c r="W23" s="30"/>
+      <c r="X23" s="30"/>
+      <c r="Y23" s="30"/>
+      <c r="Z23" s="30"/>
+      <c r="AA23" s="30"/>
+      <c r="AB23" s="30"/>
+      <c r="AC23" s="30"/>
     </row>
     <row r="24" ht="15.0" customHeight="1">
-      <c r="A24" s="29" t="s">
-        <v>351</v>
-      </c>
-      <c r="B24" s="30">
+      <c r="A24" s="31" t="s">
+        <v>352</v>
+      </c>
+      <c r="B24" s="32">
         <v>711.9</v>
       </c>
-      <c r="C24" s="30">
+      <c r="C24" s="32">
         <v>803.79</v>
       </c>
-      <c r="D24" s="30">
+      <c r="D24" s="32">
         <v>876.14</v>
       </c>
-      <c r="E24" s="30">
+      <c r="E24" s="32">
         <v>1396.67</v>
       </c>
-      <c r="F24" s="30">
+      <c r="F24" s="32">
         <v>1621.33</v>
       </c>
-      <c r="G24" s="30">
+      <c r="G24" s="32">
         <v>1915.8</v>
       </c>
-      <c r="H24" s="30">
+      <c r="H24" s="32">
         <v>1786.6</v>
       </c>
-      <c r="I24" s="30">
+      <c r="I24" s="32">
         <v>1456.41</v>
       </c>
-      <c r="J24" s="30">
+      <c r="J24" s="32">
         <v>1134.54</v>
       </c>
-      <c r="K24" s="30">
+      <c r="K24" s="32">
         <v>1298.75</v>
       </c>
-      <c r="L24" s="30">
+      <c r="L24" s="32">
         <v>479.72</v>
       </c>
-      <c r="M24" s="30">
+      <c r="M24" s="32">
         <v>381.1</v>
       </c>
-      <c r="N24" s="30">
+      <c r="N24" s="32">
         <v>282.37</v>
       </c>
-      <c r="O24" s="30">
+      <c r="O24" s="32">
         <v>186.54</v>
       </c>
-      <c r="P24" s="30">
+      <c r="P24" s="32">
         <v>159.58</v>
       </c>
-      <c r="Q24" s="30">
+      <c r="Q24" s="32">
         <v>138.0</v>
       </c>
-      <c r="R24" s="30">
+      <c r="R24" s="32">
         <v>159.65</v>
       </c>
-      <c r="S24" s="30">
+      <c r="S24" s="32">
         <v>274.6</v>
       </c>
-      <c r="T24" s="30">
+      <c r="T24" s="32">
         <v>394.13</v>
       </c>
-      <c r="U24" s="30">
+      <c r="U24" s="32">
         <v>359.55</v>
       </c>
-      <c r="V24" s="30">
+      <c r="V24" s="32">
         <v>243.61</v>
       </c>
-      <c r="W24" s="30">
+      <c r="W24" s="32">
         <v>150.78</v>
       </c>
-      <c r="X24" s="31">
+      <c r="X24" s="33">
         <v>99.89</v>
       </c>
-      <c r="Y24" s="31">
+      <c r="Y24" s="33">
         <v>94.99</v>
       </c>
-      <c r="Z24" s="30">
+      <c r="Z24" s="32">
         <v>118.71</v>
       </c>
-      <c r="AA24" s="31">
+      <c r="AA24" s="33">
         <v>65.32</v>
       </c>
-      <c r="AB24" s="31">
+      <c r="AB24" s="33">
         <v>60.61</v>
       </c>
-      <c r="AC24" s="31">
+      <c r="AC24" s="33">
         <v>94.15</v>
       </c>
     </row>
     <row r="25" ht="15.0" customHeight="1">
-      <c r="A25" s="29" t="s">
-        <v>352</v>
-      </c>
-      <c r="B25" s="30">
+      <c r="A25" s="31" t="s">
+        <v>353</v>
+      </c>
+      <c r="B25" s="32">
         <v>1163.36</v>
       </c>
-      <c r="C25" s="30">
+      <c r="C25" s="32">
         <v>1435.5</v>
       </c>
-      <c r="D25" s="30">
+      <c r="D25" s="32">
         <v>1633.74</v>
       </c>
-      <c r="E25" s="30">
+      <c r="E25" s="32">
         <v>1711.26</v>
       </c>
-      <c r="F25" s="30">
+      <c r="F25" s="32">
         <v>1603.31</v>
       </c>
-      <c r="G25" s="30">
+      <c r="G25" s="32">
         <v>1696.46</v>
       </c>
-      <c r="H25" s="30">
+      <c r="H25" s="32">
         <v>1286.75</v>
       </c>
-      <c r="I25" s="30">
+      <c r="I25" s="32">
         <v>975.89</v>
       </c>
-      <c r="J25" s="30">
+      <c r="J25" s="32">
         <v>748.08</v>
       </c>
-      <c r="K25" s="30">
+      <c r="K25" s="32">
         <v>542.74</v>
       </c>
-      <c r="L25" s="30">
+      <c r="L25" s="32">
         <v>337.97</v>
       </c>
-      <c r="M25" s="30">
+      <c r="M25" s="32">
         <v>234.84</v>
       </c>
-      <c r="N25" s="30">
+      <c r="N25" s="32">
         <v>189.39</v>
       </c>
-      <c r="O25" s="30">
+      <c r="O25" s="32">
         <v>169.21</v>
       </c>
-      <c r="P25" s="30">
+      <c r="P25" s="32">
         <v>221.72</v>
       </c>
-      <c r="Q25" s="30">
+      <c r="Q25" s="32">
         <v>262.57</v>
       </c>
-      <c r="R25" s="30">
+      <c r="R25" s="32">
         <v>300.72</v>
       </c>
-      <c r="S25" s="30">
+      <c r="S25" s="32">
         <v>292.38</v>
       </c>
-      <c r="T25" s="30">
+      <c r="T25" s="32">
         <v>239.59</v>
       </c>
-      <c r="U25" s="30">
+      <c r="U25" s="32">
         <v>194.81</v>
       </c>
-      <c r="V25" s="30">
+      <c r="V25" s="32">
         <v>139.61</v>
       </c>
-      <c r="W25" s="30">
+      <c r="W25" s="32">
         <v>110.01</v>
       </c>
-      <c r="X25" s="31">
+      <c r="X25" s="33">
         <v>91.16</v>
       </c>
-      <c r="Y25" s="31">
+      <c r="Y25" s="33">
         <v>79.17</v>
       </c>
-      <c r="Z25" s="32"/>
-      <c r="AA25" s="32"/>
-      <c r="AB25" s="32"/>
-      <c r="AC25" s="32"/>
+      <c r="Z25" s="34"/>
+      <c r="AA25" s="34"/>
+      <c r="AB25" s="34"/>
+      <c r="AC25" s="34"/>
     </row>
     <row r="26" ht="15.0" customHeight="1">
-      <c r="A26" s="27" t="s">
-        <v>353</v>
-      </c>
-      <c r="B26" s="28"/>
-      <c r="C26" s="28"/>
-      <c r="D26" s="28"/>
-      <c r="E26" s="28"/>
-      <c r="F26" s="28"/>
-      <c r="G26" s="28"/>
-      <c r="H26" s="28"/>
-      <c r="I26" s="28"/>
-      <c r="J26" s="28"/>
-      <c r="K26" s="28"/>
-      <c r="L26" s="28"/>
-      <c r="M26" s="28"/>
-      <c r="N26" s="28"/>
-      <c r="O26" s="28"/>
-      <c r="P26" s="28"/>
-      <c r="Q26" s="28"/>
-      <c r="R26" s="28"/>
-      <c r="S26" s="28"/>
-      <c r="T26" s="28"/>
-      <c r="U26" s="28"/>
-      <c r="V26" s="28"/>
-      <c r="W26" s="28"/>
-      <c r="X26" s="28"/>
-      <c r="Y26" s="28"/>
-      <c r="Z26" s="28"/>
-      <c r="AA26" s="28"/>
-      <c r="AB26" s="28"/>
-      <c r="AC26" s="28"/>
+      <c r="A26" s="29" t="s">
+        <v>354</v>
+      </c>
+      <c r="B26" s="30"/>
+      <c r="C26" s="30"/>
+      <c r="D26" s="30"/>
+      <c r="E26" s="30"/>
+      <c r="F26" s="30"/>
+      <c r="G26" s="30"/>
+      <c r="H26" s="30"/>
+      <c r="I26" s="30"/>
+      <c r="J26" s="30"/>
+      <c r="K26" s="30"/>
+      <c r="L26" s="30"/>
+      <c r="M26" s="30"/>
+      <c r="N26" s="30"/>
+      <c r="O26" s="30"/>
+      <c r="P26" s="30"/>
+      <c r="Q26" s="30"/>
+      <c r="R26" s="30"/>
+      <c r="S26" s="30"/>
+      <c r="T26" s="30"/>
+      <c r="U26" s="30"/>
+      <c r="V26" s="30"/>
+      <c r="W26" s="30"/>
+      <c r="X26" s="30"/>
+      <c r="Y26" s="30"/>
+      <c r="Z26" s="30"/>
+      <c r="AA26" s="30"/>
+      <c r="AB26" s="30"/>
+      <c r="AC26" s="30"/>
     </row>
     <row r="27" ht="15.0" customHeight="1">
-      <c r="A27" s="29" t="s">
-        <v>354</v>
-      </c>
-      <c r="B27" s="30">
+      <c r="A27" s="31" t="s">
+        <v>355</v>
+      </c>
+      <c r="B27" s="32">
         <v>376.67</v>
       </c>
-      <c r="C27" s="30">
+      <c r="C27" s="32">
         <v>425.28</v>
       </c>
-      <c r="D27" s="30">
+      <c r="D27" s="32">
         <v>463.56</v>
       </c>
-      <c r="E27" s="30">
+      <c r="E27" s="32">
         <v>738.98</v>
       </c>
-      <c r="F27" s="30">
+      <c r="F27" s="32">
         <v>857.85</v>
       </c>
-      <c r="G27" s="30">
+      <c r="G27" s="32">
         <v>1013.65</v>
       </c>
-      <c r="H27" s="30">
+      <c r="H27" s="32">
         <v>945.29</v>
       </c>
-      <c r="I27" s="30">
+      <c r="I27" s="32">
         <v>770.59</v>
       </c>
-      <c r="J27" s="30">
+      <c r="J27" s="32">
         <v>600.28</v>
       </c>
-      <c r="K27" s="30">
+      <c r="K27" s="32">
         <v>687.17</v>
       </c>
-      <c r="L27" s="30">
+      <c r="L27" s="32">
         <v>253.82</v>
       </c>
-      <c r="M27" s="30">
+      <c r="M27" s="32">
         <v>201.64</v>
       </c>
-      <c r="N27" s="30">
+      <c r="N27" s="32">
         <v>149.4</v>
       </c>
-      <c r="O27" s="31">
+      <c r="O27" s="33">
         <v>98.7</v>
       </c>
-      <c r="P27" s="31">
+      <c r="P27" s="33">
         <v>84.43</v>
       </c>
-      <c r="Q27" s="31">
+      <c r="Q27" s="33">
         <v>73.02</v>
       </c>
-      <c r="R27" s="31">
+      <c r="R27" s="33">
         <v>76.03</v>
       </c>
-      <c r="S27" s="30">
+      <c r="S27" s="32">
         <v>130.76</v>
       </c>
-      <c r="T27" s="30">
+      <c r="T27" s="32">
         <v>187.68</v>
       </c>
-      <c r="U27" s="30">
+      <c r="U27" s="32">
         <v>171.21</v>
       </c>
-      <c r="V27" s="30">
+      <c r="V27" s="32">
         <v>116.0</v>
       </c>
-      <c r="W27" s="31">
+      <c r="W27" s="33">
         <v>71.8</v>
       </c>
-      <c r="X27" s="31">
+      <c r="X27" s="33">
         <v>47.57</v>
       </c>
-      <c r="Y27" s="31">
+      <c r="Y27" s="33">
         <v>45.23</v>
       </c>
-      <c r="Z27" s="31">
+      <c r="Z27" s="33">
         <v>56.53</v>
       </c>
-      <c r="AA27" s="31">
+      <c r="AA27" s="33">
         <v>31.1</v>
       </c>
-      <c r="AB27" s="31">
+      <c r="AB27" s="33">
         <v>28.86</v>
       </c>
-      <c r="AC27" s="31">
+      <c r="AC27" s="33">
         <v>44.83</v>
       </c>
     </row>
     <row r="28" ht="15.0" customHeight="1">
-      <c r="A28" s="29" t="s">
-        <v>355</v>
-      </c>
-      <c r="B28" s="30">
+      <c r="A28" s="31" t="s">
+        <v>356</v>
+      </c>
+      <c r="B28" s="32">
         <v>615.54</v>
       </c>
-      <c r="C28" s="30">
+      <c r="C28" s="32">
         <v>759.53</v>
       </c>
-      <c r="D28" s="30">
+      <c r="D28" s="32">
         <v>864.41</v>
       </c>
-      <c r="E28" s="30">
+      <c r="E28" s="32">
         <v>905.43</v>
       </c>
-      <c r="F28" s="30">
+      <c r="F28" s="32">
         <v>848.31</v>
       </c>
-      <c r="G28" s="30">
+      <c r="G28" s="32">
         <v>897.6</v>
       </c>
-      <c r="H28" s="30">
+      <c r="H28" s="32">
         <v>680.82</v>
       </c>
-      <c r="I28" s="30">
+      <c r="I28" s="32">
         <v>516.35</v>
       </c>
-      <c r="J28" s="30">
+      <c r="J28" s="32">
         <v>395.81</v>
       </c>
-      <c r="K28" s="30">
+      <c r="K28" s="32">
         <v>287.16</v>
       </c>
-      <c r="L28" s="30">
+      <c r="L28" s="32">
         <v>178.82</v>
       </c>
-      <c r="M28" s="30">
+      <c r="M28" s="32">
         <v>124.26</v>
       </c>
-      <c r="N28" s="31">
+      <c r="N28" s="33">
         <v>98.58</v>
       </c>
-      <c r="O28" s="31">
+      <c r="O28" s="33">
         <v>85.47</v>
       </c>
-      <c r="P28" s="30">
+      <c r="P28" s="32">
         <v>108.71</v>
       </c>
-      <c r="Q28" s="30">
+      <c r="Q28" s="32">
         <v>126.49</v>
       </c>
-      <c r="R28" s="30">
+      <c r="R28" s="32">
         <v>143.2</v>
       </c>
-      <c r="S28" s="30">
+      <c r="S28" s="32">
         <v>139.23</v>
       </c>
-      <c r="T28" s="30">
+      <c r="T28" s="32">
         <v>114.09</v>
       </c>
-      <c r="U28" s="31">
+      <c r="U28" s="33">
         <v>92.77</v>
       </c>
-      <c r="V28" s="31">
+      <c r="V28" s="33">
         <v>66.48</v>
       </c>
-      <c r="W28" s="31">
+      <c r="W28" s="33">
         <v>52.38</v>
       </c>
-      <c r="X28" s="31">
+      <c r="X28" s="33">
         <v>43.41</v>
       </c>
-      <c r="Y28" s="31">
+      <c r="Y28" s="33">
         <v>37.7</v>
       </c>
-      <c r="Z28" s="32"/>
-      <c r="AA28" s="32"/>
-      <c r="AB28" s="32"/>
-      <c r="AC28" s="32"/>
+      <c r="Z28" s="34"/>
+      <c r="AA28" s="34"/>
+      <c r="AB28" s="34"/>
+      <c r="AC28" s="34"/>
     </row>
     <row r="29" ht="15.0" customHeight="1">
-      <c r="A29" s="27" t="s">
-        <v>356</v>
-      </c>
-      <c r="B29" s="28"/>
-      <c r="C29" s="28"/>
-      <c r="D29" s="28"/>
-      <c r="E29" s="28"/>
-      <c r="F29" s="28"/>
-      <c r="G29" s="28"/>
-      <c r="H29" s="28"/>
-      <c r="I29" s="28"/>
-      <c r="J29" s="28"/>
-      <c r="K29" s="28"/>
-      <c r="L29" s="28"/>
-      <c r="M29" s="28"/>
-      <c r="N29" s="28"/>
-      <c r="O29" s="28"/>
-      <c r="P29" s="28"/>
-      <c r="Q29" s="28"/>
-      <c r="R29" s="28"/>
-      <c r="S29" s="28"/>
-      <c r="T29" s="28"/>
-      <c r="U29" s="28"/>
-      <c r="V29" s="28"/>
-      <c r="W29" s="28"/>
-      <c r="X29" s="28"/>
-      <c r="Y29" s="28"/>
-      <c r="Z29" s="28"/>
-      <c r="AA29" s="28"/>
-      <c r="AB29" s="28"/>
-      <c r="AC29" s="28"/>
+      <c r="A29" s="29" t="s">
+        <v>357</v>
+      </c>
+      <c r="B29" s="30"/>
+      <c r="C29" s="30"/>
+      <c r="D29" s="30"/>
+      <c r="E29" s="30"/>
+      <c r="F29" s="30"/>
+      <c r="G29" s="30"/>
+      <c r="H29" s="30"/>
+      <c r="I29" s="30"/>
+      <c r="J29" s="30"/>
+      <c r="K29" s="30"/>
+      <c r="L29" s="30"/>
+      <c r="M29" s="30"/>
+      <c r="N29" s="30"/>
+      <c r="O29" s="30"/>
+      <c r="P29" s="30"/>
+      <c r="Q29" s="30"/>
+      <c r="R29" s="30"/>
+      <c r="S29" s="30"/>
+      <c r="T29" s="30"/>
+      <c r="U29" s="30"/>
+      <c r="V29" s="30"/>
+      <c r="W29" s="30"/>
+      <c r="X29" s="30"/>
+      <c r="Y29" s="30"/>
+      <c r="Z29" s="30"/>
+      <c r="AA29" s="30"/>
+      <c r="AB29" s="30"/>
+      <c r="AC29" s="30"/>
     </row>
     <row r="30" ht="15.0" customHeight="1">
-      <c r="A30" s="29" t="s">
-        <v>357</v>
-      </c>
-      <c r="B30" s="33">
+      <c r="A30" s="31" t="s">
+        <v>358</v>
+      </c>
+      <c r="B30" s="35">
         <v>26.41</v>
       </c>
-      <c r="C30" s="33">
+      <c r="C30" s="35">
         <v>5.18</v>
       </c>
-      <c r="D30" s="34">
+      <c r="D30" s="36">
         <v>-2.27</v>
       </c>
-      <c r="E30" s="34">
+      <c r="E30" s="36">
         <v>-3.49</v>
       </c>
-      <c r="F30" s="33">
+      <c r="F30" s="35">
         <v>0.17</v>
       </c>
-      <c r="G30" s="33">
+      <c r="G30" s="35">
         <v>2.09</v>
       </c>
-      <c r="H30" s="33">
+      <c r="H30" s="35">
         <v>0.62</v>
       </c>
-      <c r="I30" s="33">
+      <c r="I30" s="35">
         <v>1.09</v>
       </c>
-      <c r="J30" s="33">
+      <c r="J30" s="35">
         <v>0.52</v>
       </c>
-      <c r="K30" s="33">
+      <c r="K30" s="35">
         <v>2.19</v>
       </c>
-      <c r="L30" s="34">
+      <c r="L30" s="36">
         <v>-1.56</v>
       </c>
-      <c r="M30" s="33">
+      <c r="M30" s="35">
         <v>1.65</v>
       </c>
-      <c r="N30" s="33">
+      <c r="N30" s="35">
         <v>2.57</v>
       </c>
-      <c r="O30" s="33">
+      <c r="O30" s="35">
         <v>11.51</v>
       </c>
-      <c r="P30" s="33">
+      <c r="P30" s="35">
         <v>12.9</v>
       </c>
-      <c r="Q30" s="34">
+      <c r="Q30" s="36">
         <v>-18.31</v>
       </c>
-      <c r="R30" s="34">
+      <c r="R30" s="36">
         <v>-6.06</v>
       </c>
-      <c r="S30" s="34">
+      <c r="S30" s="36">
         <v>-4.8</v>
       </c>
-      <c r="T30" s="33">
+      <c r="T30" s="35">
         <v>1.54</v>
       </c>
-      <c r="U30" s="33">
+      <c r="U30" s="35">
         <v>2.11</v>
       </c>
-      <c r="V30" s="33">
+      <c r="V30" s="35">
         <v>7.73</v>
       </c>
-      <c r="W30" s="33">
+      <c r="W30" s="35">
         <v>7.22</v>
       </c>
-      <c r="X30" s="33">
+      <c r="X30" s="35">
         <v>20.09</v>
       </c>
-      <c r="Y30" s="33">
+      <c r="Y30" s="35">
         <v>27.0</v>
       </c>
-      <c r="Z30" s="33">
+      <c r="Z30" s="35">
         <v>6.35</v>
       </c>
-      <c r="AA30" s="33">
+      <c r="AA30" s="35">
         <v>20.13</v>
       </c>
-      <c r="AB30" s="34">
+      <c r="AB30" s="36">
         <v>-17.34</v>
       </c>
-      <c r="AC30" s="33">
+      <c r="AC30" s="35">
         <v>2.92</v>
       </c>
     </row>
     <row r="31" ht="15.0" customHeight="1">
-      <c r="A31" s="29" t="s">
-        <v>358</v>
-      </c>
-      <c r="B31" s="33">
+      <c r="A31" s="31" t="s">
+        <v>359</v>
+      </c>
+      <c r="B31" s="35">
         <v>2.73</v>
       </c>
-      <c r="C31" s="33">
+      <c r="C31" s="35">
         <v>0.19</v>
       </c>
-      <c r="D31" s="34">
+      <c r="D31" s="36">
         <v>-0.18</v>
       </c>
-      <c r="E31" s="33">
+      <c r="E31" s="35">
         <v>0.27</v>
       </c>
-      <c r="F31" s="33">
+      <c r="F31" s="35">
         <v>0.93</v>
       </c>
-      <c r="G31" s="33">
+      <c r="G31" s="35">
         <v>1.32</v>
       </c>
-      <c r="H31" s="33">
+      <c r="H31" s="35">
         <v>0.89</v>
       </c>
-      <c r="I31" s="33">
+      <c r="I31" s="35">
         <v>1.06</v>
       </c>
-      <c r="J31" s="33">
+      <c r="J31" s="35">
         <v>1.18</v>
       </c>
-      <c r="K31" s="33">
+      <c r="K31" s="35">
         <v>2.31</v>
       </c>
-      <c r="L31" s="33">
+      <c r="L31" s="35">
         <v>3.61</v>
       </c>
-      <c r="M31" s="33">
+      <c r="M31" s="35">
         <v>2.8</v>
       </c>
-      <c r="N31" s="33">
+      <c r="N31" s="35">
         <v>1.96</v>
       </c>
-      <c r="O31" s="34">
+      <c r="O31" s="36">
         <v>-0.08</v>
       </c>
-      <c r="P31" s="34">
+      <c r="P31" s="36">
         <v>-1.76</v>
       </c>
-      <c r="Q31" s="34">
+      <c r="Q31" s="36">
         <v>-2.74</v>
       </c>
-      <c r="R31" s="33">
+      <c r="R31" s="35">
         <v>0.77</v>
       </c>
-      <c r="S31" s="33">
+      <c r="S31" s="35">
         <v>2.15</v>
       </c>
-      <c r="T31" s="33">
+      <c r="T31" s="35">
         <v>5.03</v>
       </c>
-      <c r="U31" s="33">
+      <c r="U31" s="35">
         <v>8.98</v>
       </c>
-      <c r="V31" s="33">
+      <c r="V31" s="35">
         <v>11.9</v>
       </c>
-      <c r="W31" s="33">
+      <c r="W31" s="35">
         <v>14.87</v>
       </c>
-      <c r="X31" s="33">
+      <c r="X31" s="35">
         <v>13.08</v>
       </c>
-      <c r="Y31" s="33">
+      <c r="Y31" s="35">
         <v>9.46</v>
       </c>
-      <c r="Z31" s="33"/>
-      <c r="AA31" s="33"/>
-      <c r="AB31" s="33"/>
-      <c r="AC31" s="33"/>
+      <c r="Z31" s="35"/>
+      <c r="AA31" s="35"/>
+      <c r="AB31" s="35"/>
+      <c r="AC31" s="35"/>
     </row>
     <row r="32" ht="15.0" customHeight="1">
-      <c r="A32" s="27" t="s">
-        <v>359</v>
-      </c>
-      <c r="B32" s="28"/>
-      <c r="C32" s="28"/>
-      <c r="D32" s="28"/>
-      <c r="E32" s="28"/>
-      <c r="F32" s="28"/>
-      <c r="G32" s="28"/>
-      <c r="H32" s="28"/>
-      <c r="I32" s="28"/>
-      <c r="J32" s="28"/>
-      <c r="K32" s="28"/>
-      <c r="L32" s="28"/>
-      <c r="M32" s="28"/>
-      <c r="N32" s="28"/>
-      <c r="O32" s="28"/>
-      <c r="P32" s="28"/>
-      <c r="Q32" s="28"/>
-      <c r="R32" s="28"/>
-      <c r="S32" s="28"/>
-      <c r="T32" s="28"/>
-      <c r="U32" s="28"/>
-      <c r="V32" s="28"/>
-      <c r="W32" s="28"/>
-      <c r="X32" s="28"/>
-      <c r="Y32" s="28"/>
-      <c r="Z32" s="28"/>
-      <c r="AA32" s="28"/>
-      <c r="AB32" s="28"/>
-      <c r="AC32" s="28"/>
+      <c r="A32" s="29" t="s">
+        <v>360</v>
+      </c>
+      <c r="B32" s="30"/>
+      <c r="C32" s="30"/>
+      <c r="D32" s="30"/>
+      <c r="E32" s="30"/>
+      <c r="F32" s="30"/>
+      <c r="G32" s="30"/>
+      <c r="H32" s="30"/>
+      <c r="I32" s="30"/>
+      <c r="J32" s="30"/>
+      <c r="K32" s="30"/>
+      <c r="L32" s="30"/>
+      <c r="M32" s="30"/>
+      <c r="N32" s="30"/>
+      <c r="O32" s="30"/>
+      <c r="P32" s="30"/>
+      <c r="Q32" s="30"/>
+      <c r="R32" s="30"/>
+      <c r="S32" s="30"/>
+      <c r="T32" s="30"/>
+      <c r="U32" s="30"/>
+      <c r="V32" s="30"/>
+      <c r="W32" s="30"/>
+      <c r="X32" s="30"/>
+      <c r="Y32" s="30"/>
+      <c r="Z32" s="30"/>
+      <c r="AA32" s="30"/>
+      <c r="AB32" s="30"/>
+      <c r="AC32" s="30"/>
     </row>
     <row r="33" ht="15.0" customHeight="1">
-      <c r="A33" s="29" t="s">
-        <v>360</v>
-      </c>
-      <c r="B33" s="33">
+      <c r="A33" s="31" t="s">
+        <v>361</v>
+      </c>
+      <c r="B33" s="35">
         <v>0.0</v>
       </c>
-      <c r="C33" s="33">
+      <c r="C33" s="35">
         <v>0.0</v>
       </c>
-      <c r="D33" s="33">
+      <c r="D33" s="35">
         <v>3.51</v>
       </c>
-      <c r="E33" s="33">
+      <c r="E33" s="35">
         <v>1.89</v>
       </c>
-      <c r="F33" s="33">
+      <c r="F33" s="35">
         <v>0.79</v>
       </c>
-      <c r="G33" s="33">
+      <c r="G33" s="35">
         <v>1.52</v>
       </c>
-      <c r="H33" s="33">
+      <c r="H33" s="35">
         <v>1.33</v>
       </c>
-      <c r="I33" s="33">
+      <c r="I33" s="35">
         <v>1.26</v>
       </c>
-      <c r="J33" s="33">
+      <c r="J33" s="35">
         <v>1.53</v>
       </c>
-      <c r="K33" s="33">
+      <c r="K33" s="35">
         <v>0.96</v>
       </c>
-      <c r="L33" s="33">
+      <c r="L33" s="35">
         <v>2.64</v>
       </c>
-      <c r="M33" s="33">
+      <c r="M33" s="35">
         <v>2.57</v>
       </c>
-      <c r="N33" s="33"/>
-      <c r="O33" s="33">
+      <c r="N33" s="35"/>
+      <c r="O33" s="35">
         <v>3.06</v>
       </c>
-      <c r="P33" s="33">
+      <c r="P33" s="35">
         <v>2.93</v>
       </c>
-      <c r="Q33" s="33">
+      <c r="Q33" s="35">
         <v>0.0</v>
       </c>
-      <c r="R33" s="33">
+      <c r="R33" s="35">
         <v>4.3</v>
       </c>
-      <c r="S33" s="33">
+      <c r="S33" s="35">
         <v>2.68</v>
       </c>
-      <c r="T33" s="33">
+      <c r="T33" s="35">
         <v>1.58</v>
       </c>
-      <c r="U33" s="33">
+      <c r="U33" s="35">
         <v>1.87</v>
       </c>
-      <c r="V33" s="33">
+      <c r="V33" s="35">
         <v>1.96</v>
       </c>
-      <c r="W33" s="33">
+      <c r="W33" s="35">
         <v>2.24</v>
       </c>
-      <c r="X33" s="33">
+      <c r="X33" s="35">
         <v>3.35</v>
       </c>
-      <c r="Y33" s="33">
+      <c r="Y33" s="35">
         <v>2.82</v>
       </c>
-      <c r="Z33" s="33">
+      <c r="Z33" s="35">
         <v>2.31</v>
       </c>
-      <c r="AA33" s="33">
+      <c r="AA33" s="35">
         <v>0.0</v>
       </c>
-      <c r="AB33" s="33">
+      <c r="AB33" s="35">
         <v>0.53</v>
       </c>
-      <c r="AC33" s="33">
+      <c r="AC33" s="35">
         <v>1.95</v>
       </c>
     </row>
     <row r="34" ht="15.0" customHeight="1">
-      <c r="A34" s="29" t="s">
-        <v>361</v>
-      </c>
-      <c r="B34" s="33">
+      <c r="A34" s="31" t="s">
+        <v>362</v>
+      </c>
+      <c r="B34" s="35">
         <v>1.3</v>
       </c>
-      <c r="C34" s="33">
+      <c r="C34" s="35">
         <v>1.49</v>
       </c>
-      <c r="D34" s="33">
+      <c r="D34" s="35">
         <v>1.59</v>
       </c>
-      <c r="E34" s="33">
+      <c r="E34" s="35">
         <v>1.34</v>
       </c>
-      <c r="F34" s="33">
+      <c r="F34" s="35">
         <v>1.28</v>
       </c>
-      <c r="G34" s="33">
+      <c r="G34" s="35">
         <v>1.32</v>
       </c>
-      <c r="H34" s="33">
+      <c r="H34" s="35">
         <v>1.37</v>
       </c>
-      <c r="I34" s="33">
+      <c r="I34" s="35">
         <v>1.49</v>
       </c>
-      <c r="J34" s="33"/>
-      <c r="K34" s="33"/>
-      <c r="L34" s="33"/>
-      <c r="M34" s="33"/>
-      <c r="N34" s="33"/>
-      <c r="O34" s="33">
+      <c r="J34" s="35"/>
+      <c r="K34" s="35"/>
+      <c r="L34" s="35"/>
+      <c r="M34" s="35"/>
+      <c r="N34" s="35"/>
+      <c r="O34" s="35">
         <v>2.64</v>
       </c>
-      <c r="P34" s="33">
+      <c r="P34" s="35">
         <v>2.19</v>
       </c>
-      <c r="Q34" s="33">
+      <c r="Q34" s="35">
         <v>2.0</v>
       </c>
-      <c r="R34" s="33">
+      <c r="R34" s="35">
         <v>2.21</v>
       </c>
-      <c r="S34" s="33">
+      <c r="S34" s="35">
         <v>1.99</v>
       </c>
-      <c r="T34" s="33">
+      <c r="T34" s="35">
         <v>1.95</v>
       </c>
-      <c r="U34" s="33">
+      <c r="U34" s="35">
         <v>2.21</v>
       </c>
-      <c r="V34" s="33">
+      <c r="V34" s="35">
         <v>2.39</v>
       </c>
-      <c r="W34" s="33">
+      <c r="W34" s="35">
         <v>2.3</v>
       </c>
-      <c r="X34" s="33">
+      <c r="X34" s="35">
         <v>2.08</v>
       </c>
-      <c r="Y34" s="33">
+      <c r="Y34" s="35">
         <v>1.77</v>
       </c>
-      <c r="Z34" s="33"/>
-      <c r="AA34" s="33"/>
-      <c r="AB34" s="33"/>
-      <c r="AC34" s="33"/>
+      <c r="Z34" s="35"/>
+      <c r="AA34" s="35"/>
+      <c r="AB34" s="35"/>
+      <c r="AC34" s="35"/>
     </row>
     <row r="35" ht="15.0" customHeight="1">
-      <c r="A35" s="29" t="s">
-        <v>362</v>
-      </c>
-      <c r="B35" s="33">
+      <c r="A35" s="31" t="s">
+        <v>363</v>
+      </c>
+      <c r="B35" s="35">
         <v>0.0</v>
       </c>
-      <c r="C35" s="33">
+      <c r="C35" s="35">
         <v>0.0</v>
       </c>
-      <c r="D35" s="33">
+      <c r="D35" s="35">
         <v>3.51</v>
       </c>
-      <c r="E35" s="33">
+      <c r="E35" s="35">
         <v>1.89</v>
       </c>
-      <c r="F35" s="33">
+      <c r="F35" s="35">
         <v>0.79</v>
       </c>
-      <c r="G35" s="33">
+      <c r="G35" s="35">
         <v>1.52</v>
       </c>
-      <c r="H35" s="33">
+      <c r="H35" s="35">
         <v>1.33</v>
       </c>
-      <c r="I35" s="33">
+      <c r="I35" s="35">
         <v>1.26</v>
       </c>
-      <c r="J35" s="33">
+      <c r="J35" s="35">
         <v>1.53</v>
       </c>
-      <c r="K35" s="33">
+      <c r="K35" s="35">
         <v>0.96</v>
       </c>
-      <c r="L35" s="33">
+      <c r="L35" s="35">
         <v>2.64</v>
       </c>
-      <c r="M35" s="33">
+      <c r="M35" s="35">
         <v>2.57</v>
       </c>
-      <c r="N35" s="33">
+      <c r="N35" s="35">
         <v>3.28</v>
       </c>
-      <c r="O35" s="33">
+      <c r="O35" s="35">
         <v>4.25</v>
       </c>
-      <c r="P35" s="33">
+      <c r="P35" s="35">
         <v>4.06</v>
       </c>
-      <c r="Q35" s="33">
+      <c r="Q35" s="35">
         <v>0.0</v>
       </c>
-      <c r="R35" s="33">
+      <c r="R35" s="35">
         <v>5.97</v>
       </c>
-      <c r="S35" s="33">
+      <c r="S35" s="35">
         <v>3.73</v>
       </c>
-      <c r="T35" s="33">
+      <c r="T35" s="35">
         <v>2.2</v>
       </c>
-      <c r="U35" s="33">
+      <c r="U35" s="35">
         <v>2.6</v>
       </c>
-      <c r="V35" s="33">
+      <c r="V35" s="35">
         <v>2.73</v>
       </c>
-      <c r="W35" s="33">
+      <c r="W35" s="35">
         <v>3.12</v>
       </c>
-      <c r="X35" s="33">
+      <c r="X35" s="35">
         <v>4.65</v>
       </c>
-      <c r="Y35" s="33">
+      <c r="Y35" s="35">
         <v>3.91</v>
       </c>
-      <c r="Z35" s="33">
+      <c r="Z35" s="35">
         <v>3.08</v>
       </c>
-      <c r="AA35" s="33">
+      <c r="AA35" s="35">
         <v>0.0</v>
       </c>
-      <c r="AB35" s="33">
+      <c r="AB35" s="35">
         <v>0.0</v>
       </c>
-      <c r="AC35" s="33">
+      <c r="AC35" s="35">
         <v>2.6</v>
       </c>
     </row>
     <row r="36" ht="15.0" customHeight="1">
-      <c r="A36" s="29" t="s">
-        <v>363</v>
-      </c>
-      <c r="B36" s="33">
+      <c r="A36" s="31" t="s">
+        <v>364</v>
+      </c>
+      <c r="B36" s="35">
         <v>1.3</v>
       </c>
-      <c r="C36" s="33">
+      <c r="C36" s="35">
         <v>1.49</v>
       </c>
-      <c r="D36" s="33">
+      <c r="D36" s="35">
         <v>1.59</v>
       </c>
-      <c r="E36" s="33">
+      <c r="E36" s="35">
         <v>1.34</v>
       </c>
-      <c r="F36" s="33">
+      <c r="F36" s="35">
         <v>1.28</v>
       </c>
-      <c r="G36" s="33">
+      <c r="G36" s="35">
         <v>1.32</v>
       </c>
-      <c r="H36" s="33">
+      <c r="H36" s="35">
         <v>1.37</v>
       </c>
-      <c r="I36" s="33">
+      <c r="I36" s="35">
         <v>1.49</v>
       </c>
-      <c r="J36" s="33">
+      <c r="J36" s="35">
         <v>1.74</v>
       </c>
-      <c r="K36" s="33">
+      <c r="K36" s="35">
         <v>2.04</v>
       </c>
-      <c r="L36" s="33">
+      <c r="L36" s="35">
         <v>3.14</v>
       </c>
-      <c r="M36" s="33">
+      <c r="M36" s="35">
         <v>2.94</v>
       </c>
-      <c r="N36" s="33">
+      <c r="N36" s="35">
         <v>3.54</v>
       </c>
-      <c r="O36" s="33">
+      <c r="O36" s="35">
         <v>3.67</v>
       </c>
-      <c r="P36" s="33">
+      <c r="P36" s="35">
         <v>3.04</v>
       </c>
-      <c r="Q36" s="33">
+      <c r="Q36" s="35">
         <v>2.78</v>
       </c>
-      <c r="R36" s="33">
+      <c r="R36" s="35">
         <v>3.07</v>
       </c>
-      <c r="S36" s="33">
+      <c r="S36" s="35">
         <v>2.77</v>
       </c>
-      <c r="T36" s="33">
+      <c r="T36" s="35">
         <v>2.71</v>
       </c>
-      <c r="U36" s="33">
+      <c r="U36" s="35">
         <v>3.07</v>
       </c>
-      <c r="V36" s="33">
+      <c r="V36" s="35">
         <v>3.3</v>
       </c>
-      <c r="W36" s="33">
+      <c r="W36" s="35">
         <v>3.16</v>
       </c>
-      <c r="X36" s="33">
+      <c r="X36" s="35">
         <v>2.75</v>
       </c>
-      <c r="Y36" s="33">
+      <c r="Y36" s="35">
         <v>2.3</v>
       </c>
-      <c r="Z36" s="33"/>
-      <c r="AA36" s="33"/>
-      <c r="AB36" s="33"/>
-      <c r="AC36" s="33"/>
+      <c r="Z36" s="35"/>
+      <c r="AA36" s="35"/>
+      <c r="AB36" s="35"/>
+      <c r="AC36" s="35"/>
     </row>
     <row r="37" ht="15.0" customHeight="1">
-      <c r="A37" s="27" t="s">
-        <v>364</v>
-      </c>
-      <c r="B37" s="28"/>
-      <c r="C37" s="28"/>
-      <c r="D37" s="28"/>
-      <c r="E37" s="28"/>
-      <c r="F37" s="28"/>
-      <c r="G37" s="28"/>
-      <c r="H37" s="28"/>
-      <c r="I37" s="28"/>
-      <c r="J37" s="28"/>
-      <c r="K37" s="28"/>
-      <c r="L37" s="28"/>
-      <c r="M37" s="28"/>
-      <c r="N37" s="28"/>
-      <c r="O37" s="28"/>
-      <c r="P37" s="28"/>
-      <c r="Q37" s="28"/>
-      <c r="R37" s="28"/>
-      <c r="S37" s="28"/>
-      <c r="T37" s="28"/>
-      <c r="U37" s="28"/>
-      <c r="V37" s="28"/>
-      <c r="W37" s="28"/>
-      <c r="X37" s="28"/>
-      <c r="Y37" s="28"/>
-      <c r="Z37" s="28"/>
-      <c r="AA37" s="28"/>
-      <c r="AB37" s="28"/>
-      <c r="AC37" s="28"/>
+      <c r="A37" s="29" t="s">
+        <v>365</v>
+      </c>
+      <c r="B37" s="30"/>
+      <c r="C37" s="30"/>
+      <c r="D37" s="30"/>
+      <c r="E37" s="30"/>
+      <c r="F37" s="30"/>
+      <c r="G37" s="30"/>
+      <c r="H37" s="30"/>
+      <c r="I37" s="30"/>
+      <c r="J37" s="30"/>
+      <c r="K37" s="30"/>
+      <c r="L37" s="30"/>
+      <c r="M37" s="30"/>
+      <c r="N37" s="30"/>
+      <c r="O37" s="30"/>
+      <c r="P37" s="30"/>
+      <c r="Q37" s="30"/>
+      <c r="R37" s="30"/>
+      <c r="S37" s="30"/>
+      <c r="T37" s="30"/>
+      <c r="U37" s="30"/>
+      <c r="V37" s="30"/>
+      <c r="W37" s="30"/>
+      <c r="X37" s="30"/>
+      <c r="Y37" s="30"/>
+      <c r="Z37" s="30"/>
+      <c r="AA37" s="30"/>
+      <c r="AB37" s="30"/>
+      <c r="AC37" s="30"/>
     </row>
     <row r="38" ht="15.0" customHeight="1">
-      <c r="A38" s="29" t="s">
-        <v>365</v>
-      </c>
-      <c r="B38" s="31">
+      <c r="A38" s="31" t="s">
+        <v>366</v>
+      </c>
+      <c r="B38" s="33">
         <v>1.72</v>
       </c>
-      <c r="C38" s="31">
+      <c r="C38" s="33">
         <v>1.95</v>
       </c>
-      <c r="D38" s="31">
+      <c r="D38" s="33">
         <v>1.77</v>
       </c>
-      <c r="E38" s="31">
+      <c r="E38" s="33">
         <v>2.71</v>
       </c>
-      <c r="F38" s="31">
+      <c r="F38" s="33">
         <v>3.7</v>
       </c>
-      <c r="G38" s="31">
+      <c r="G38" s="33">
         <v>4.6</v>
       </c>
-      <c r="H38" s="31">
+      <c r="H38" s="33">
         <v>4.79</v>
       </c>
-      <c r="I38" s="31">
+      <c r="I38" s="33">
         <v>4.6</v>
       </c>
-      <c r="J38" s="31">
+      <c r="J38" s="33">
         <v>4.06</v>
       </c>
-      <c r="K38" s="31">
+      <c r="K38" s="33">
         <v>5.34</v>
       </c>
-      <c r="L38" s="31">
+      <c r="L38" s="33">
         <v>2.11</v>
       </c>
-      <c r="M38" s="31">
+      <c r="M38" s="33">
         <v>2.11</v>
       </c>
-      <c r="N38" s="31">
+      <c r="N38" s="33">
         <v>1.66</v>
       </c>
-      <c r="O38" s="31">
+      <c r="O38" s="33">
         <v>1.29</v>
       </c>
-      <c r="P38" s="31">
+      <c r="P38" s="33">
         <v>1.11</v>
       </c>
-      <c r="Q38" s="31">
+      <c r="Q38" s="33">
         <v>1.02</v>
       </c>
-      <c r="R38" s="31">
+      <c r="R38" s="33">
         <v>1.1</v>
       </c>
-      <c r="S38" s="31">
+      <c r="S38" s="33">
         <v>1.83</v>
       </c>
-      <c r="T38" s="31">
+      <c r="T38" s="33">
         <v>3.04</v>
       </c>
-      <c r="U38" s="31">
+      <c r="U38" s="33">
         <v>2.86</v>
       </c>
-      <c r="V38" s="31">
+      <c r="V38" s="33">
         <v>2.19</v>
       </c>
-      <c r="W38" s="31">
+      <c r="W38" s="33">
         <v>1.43</v>
       </c>
-      <c r="X38" s="31">
+      <c r="X38" s="33">
         <v>1.05</v>
       </c>
-      <c r="Y38" s="31">
+      <c r="Y38" s="33">
         <v>1.23</v>
       </c>
-      <c r="Z38" s="31">
+      <c r="Z38" s="33">
         <v>1.54</v>
       </c>
-      <c r="AA38" s="31">
+      <c r="AA38" s="33">
         <v>1.12</v>
       </c>
-      <c r="AB38" s="31">
+      <c r="AB38" s="33">
         <v>1.13</v>
       </c>
-      <c r="AC38" s="31">
+      <c r="AC38" s="33">
         <v>1.65</v>
       </c>
     </row>
     <row r="39" ht="15.0" customHeight="1">
-      <c r="A39" s="29" t="s">
-        <v>366</v>
-      </c>
-      <c r="B39" s="31">
+      <c r="A39" s="31" t="s">
+        <v>367</v>
+      </c>
+      <c r="B39" s="33">
         <v>2.42</v>
       </c>
-      <c r="C39" s="31">
+      <c r="C39" s="33">
         <v>2.94</v>
       </c>
-      <c r="D39" s="31">
+      <c r="D39" s="33">
         <v>3.43</v>
       </c>
-      <c r="E39" s="31">
+      <c r="E39" s="33">
         <v>3.99</v>
       </c>
-      <c r="F39" s="31">
+      <c r="F39" s="33">
         <v>4.34</v>
       </c>
-      <c r="G39" s="31">
+      <c r="G39" s="33">
         <v>4.67</v>
       </c>
-      <c r="H39" s="31">
+      <c r="H39" s="33">
         <v>4.28</v>
       </c>
-      <c r="I39" s="31">
+      <c r="I39" s="33">
         <v>3.79</v>
       </c>
-      <c r="J39" s="31">
+      <c r="J39" s="33">
         <v>3.21</v>
       </c>
-      <c r="K39" s="31">
+      <c r="K39" s="33">
         <v>2.65</v>
       </c>
-      <c r="L39" s="31">
+      <c r="L39" s="33">
         <v>1.69</v>
       </c>
-      <c r="M39" s="31">
+      <c r="M39" s="33">
         <v>1.47</v>
       </c>
-      <c r="N39" s="31">
+      <c r="N39" s="33">
         <v>1.26</v>
       </c>
-      <c r="O39" s="31">
+      <c r="O39" s="33">
         <v>1.27</v>
       </c>
-      <c r="P39" s="31">
+      <c r="P39" s="33">
         <v>1.59</v>
       </c>
-      <c r="Q39" s="31">
+      <c r="Q39" s="33">
         <v>1.93</v>
       </c>
-      <c r="R39" s="31">
+      <c r="R39" s="33">
         <v>2.18</v>
       </c>
-      <c r="S39" s="31">
+      <c r="S39" s="33">
         <v>2.3</v>
       </c>
-      <c r="T39" s="31">
+      <c r="T39" s="33">
         <v>2.22</v>
       </c>
-      <c r="U39" s="31">
+      <c r="U39" s="33">
         <v>1.84</v>
       </c>
-      <c r="V39" s="31">
+      <c r="V39" s="33">
         <v>1.52</v>
       </c>
-      <c r="W39" s="31">
+      <c r="W39" s="33">
         <v>1.28</v>
       </c>
-      <c r="X39" s="31">
+      <c r="X39" s="33">
         <v>1.22</v>
       </c>
-      <c r="Y39" s="31">
+      <c r="Y39" s="33">
         <v>1.33</v>
       </c>
-      <c r="Z39" s="32"/>
-      <c r="AA39" s="32"/>
-      <c r="AB39" s="32"/>
-      <c r="AC39" s="32"/>
+      <c r="Z39" s="34"/>
+      <c r="AA39" s="34"/>
+      <c r="AB39" s="34"/>
+      <c r="AC39" s="34"/>
     </row>
     <row r="40" ht="15.0" customHeight="1">
-      <c r="A40" s="27" t="s">
-        <v>367</v>
-      </c>
-      <c r="B40" s="28"/>
-      <c r="C40" s="28"/>
-      <c r="D40" s="28"/>
-      <c r="E40" s="28"/>
-      <c r="F40" s="28"/>
-      <c r="G40" s="28"/>
-      <c r="H40" s="28"/>
-      <c r="I40" s="28"/>
-      <c r="J40" s="28"/>
-      <c r="K40" s="28"/>
-      <c r="L40" s="28"/>
-      <c r="M40" s="28"/>
-      <c r="N40" s="28"/>
-      <c r="O40" s="28"/>
-      <c r="P40" s="28"/>
-      <c r="Q40" s="28"/>
-      <c r="R40" s="28"/>
-      <c r="S40" s="28"/>
-      <c r="T40" s="28"/>
-      <c r="U40" s="28"/>
-      <c r="V40" s="28"/>
-      <c r="W40" s="28"/>
-      <c r="X40" s="28"/>
-      <c r="Y40" s="28"/>
-      <c r="Z40" s="28"/>
-      <c r="AA40" s="28"/>
-      <c r="AB40" s="28"/>
-      <c r="AC40" s="28"/>
+      <c r="A40" s="29" t="s">
+        <v>368</v>
+      </c>
+      <c r="B40" s="30"/>
+      <c r="C40" s="30"/>
+      <c r="D40" s="30"/>
+      <c r="E40" s="30"/>
+      <c r="F40" s="30"/>
+      <c r="G40" s="30"/>
+      <c r="H40" s="30"/>
+      <c r="I40" s="30"/>
+      <c r="J40" s="30"/>
+      <c r="K40" s="30"/>
+      <c r="L40" s="30"/>
+      <c r="M40" s="30"/>
+      <c r="N40" s="30"/>
+      <c r="O40" s="30"/>
+      <c r="P40" s="30"/>
+      <c r="Q40" s="30"/>
+      <c r="R40" s="30"/>
+      <c r="S40" s="30"/>
+      <c r="T40" s="30"/>
+      <c r="U40" s="30"/>
+      <c r="V40" s="30"/>
+      <c r="W40" s="30"/>
+      <c r="X40" s="30"/>
+      <c r="Y40" s="30"/>
+      <c r="Z40" s="30"/>
+      <c r="AA40" s="30"/>
+      <c r="AB40" s="30"/>
+      <c r="AC40" s="30"/>
     </row>
     <row r="41" ht="15.0" customHeight="1">
-      <c r="A41" s="29" t="s">
-        <v>368</v>
-      </c>
-      <c r="B41" s="31">
+      <c r="A41" s="31" t="s">
+        <v>369</v>
+      </c>
+      <c r="B41" s="33">
         <v>2.26</v>
       </c>
-      <c r="C41" s="31">
+      <c r="C41" s="33">
         <v>2.62</v>
       </c>
-      <c r="D41" s="31">
+      <c r="D41" s="33">
         <v>2.6</v>
       </c>
-      <c r="E41" s="31">
+      <c r="E41" s="33">
         <v>3.75</v>
       </c>
-      <c r="F41" s="31">
+      <c r="F41" s="33">
         <v>5.3</v>
       </c>
-      <c r="G41" s="31">
+      <c r="G41" s="33">
         <v>6.96</v>
       </c>
-      <c r="H41" s="31">
+      <c r="H41" s="33">
         <v>7.0</v>
       </c>
-      <c r="I41" s="31">
+      <c r="I41" s="33">
         <v>5.87</v>
       </c>
-      <c r="J41" s="31">
+      <c r="J41" s="33">
         <v>5.36</v>
       </c>
-      <c r="K41" s="31">
+      <c r="K41" s="33">
         <v>5.83</v>
       </c>
-      <c r="L41" s="31">
+      <c r="L41" s="33">
         <v>2.34</v>
       </c>
-      <c r="M41" s="31">
+      <c r="M41" s="33">
         <v>2.3</v>
       </c>
-      <c r="N41" s="31">
+      <c r="N41" s="33">
         <v>1.79</v>
       </c>
-      <c r="O41" s="31">
+      <c r="O41" s="33">
         <v>1.38</v>
       </c>
-      <c r="P41" s="31">
+      <c r="P41" s="33">
         <v>1.17</v>
       </c>
-      <c r="Q41" s="31">
+      <c r="Q41" s="33">
         <v>1.04</v>
       </c>
-      <c r="R41" s="31">
+      <c r="R41" s="33">
         <v>1.13</v>
       </c>
-      <c r="S41" s="31">
+      <c r="S41" s="33">
         <v>1.9</v>
       </c>
-      <c r="T41" s="31">
+      <c r="T41" s="33">
         <v>3.16</v>
       </c>
-      <c r="U41" s="31">
+      <c r="U41" s="33">
         <v>2.93</v>
       </c>
-      <c r="V41" s="31">
+      <c r="V41" s="33">
         <v>2.23</v>
       </c>
-      <c r="W41" s="31">
+      <c r="W41" s="33">
         <v>1.43</v>
       </c>
-      <c r="X41" s="31">
+      <c r="X41" s="33">
         <v>1.05</v>
       </c>
-      <c r="Y41" s="31">
+      <c r="Y41" s="33">
         <v>1.23</v>
       </c>
-      <c r="Z41" s="31">
+      <c r="Z41" s="33">
         <v>1.54</v>
       </c>
-      <c r="AA41" s="31">
+      <c r="AA41" s="33">
         <v>1.12</v>
       </c>
-      <c r="AB41" s="31">
+      <c r="AB41" s="33">
         <v>1.13</v>
       </c>
-      <c r="AC41" s="31">
+      <c r="AC41" s="33">
         <v>1.65</v>
       </c>
     </row>
     <row r="42" ht="15.0" customHeight="1">
-      <c r="A42" s="29" t="s">
-        <v>369</v>
-      </c>
-      <c r="B42" s="31">
+      <c r="A42" s="31" t="s">
+        <v>370</v>
+      </c>
+      <c r="B42" s="33">
         <v>3.36</v>
       </c>
-      <c r="C42" s="31">
+      <c r="C42" s="33">
         <v>4.19</v>
       </c>
-      <c r="D42" s="31">
+      <c r="D42" s="33">
         <v>4.96</v>
       </c>
-      <c r="E42" s="31">
+      <c r="E42" s="33">
         <v>5.63</v>
       </c>
-      <c r="F42" s="31">
+      <c r="F42" s="33">
         <v>6.08</v>
       </c>
-      <c r="G42" s="31">
+      <c r="G42" s="33">
         <v>6.22</v>
       </c>
-      <c r="H42" s="31">
+      <c r="H42" s="33">
         <v>5.38</v>
       </c>
-      <c r="I42" s="31">
+      <c r="I42" s="33">
         <v>4.47</v>
       </c>
-      <c r="J42" s="31">
+      <c r="J42" s="33">
         <v>3.65</v>
       </c>
-      <c r="K42" s="31">
+      <c r="K42" s="33">
         <v>2.88</v>
       </c>
-      <c r="L42" s="31">
+      <c r="L42" s="33">
         <v>1.83</v>
       </c>
-      <c r="M42" s="31">
+      <c r="M42" s="33">
         <v>1.57</v>
       </c>
-      <c r="N42" s="31">
+      <c r="N42" s="33">
         <v>1.32</v>
       </c>
-      <c r="O42" s="31">
+      <c r="O42" s="33">
         <v>1.32</v>
       </c>
-      <c r="P42" s="31">
+      <c r="P42" s="33">
         <v>1.65</v>
       </c>
-      <c r="Q42" s="31">
+      <c r="Q42" s="33">
         <v>1.99</v>
       </c>
-      <c r="R42" s="31">
+      <c r="R42" s="33">
         <v>2.25</v>
       </c>
-      <c r="S42" s="31">
+      <c r="S42" s="33">
         <v>2.36</v>
       </c>
-      <c r="T42" s="31">
+      <c r="T42" s="33">
         <v>2.26</v>
       </c>
-      <c r="U42" s="31">
+      <c r="U42" s="33">
         <v>1.85</v>
       </c>
-      <c r="V42" s="31">
+      <c r="V42" s="33">
         <v>1.53</v>
       </c>
-      <c r="W42" s="31">
+      <c r="W42" s="33">
         <v>1.28</v>
       </c>
-      <c r="X42" s="31">
+      <c r="X42" s="33">
         <v>1.22</v>
       </c>
-      <c r="Y42" s="31">
+      <c r="Y42" s="33">
         <v>1.33</v>
       </c>
-      <c r="Z42" s="32"/>
-      <c r="AA42" s="32"/>
-      <c r="AB42" s="32"/>
-      <c r="AC42" s="32"/>
+      <c r="Z42" s="34"/>
+      <c r="AA42" s="34"/>
+      <c r="AB42" s="34"/>
+      <c r="AC42" s="34"/>
     </row>
     <row r="43" ht="15.0" customHeight="1">
-      <c r="A43" s="27" t="s">
-        <v>370</v>
-      </c>
-      <c r="B43" s="28"/>
-      <c r="C43" s="28"/>
-      <c r="D43" s="28"/>
-      <c r="E43" s="28"/>
-      <c r="F43" s="28"/>
-      <c r="G43" s="28"/>
-      <c r="H43" s="28"/>
-      <c r="I43" s="28"/>
-      <c r="J43" s="28"/>
-      <c r="K43" s="28"/>
-      <c r="L43" s="28"/>
-      <c r="M43" s="28"/>
-      <c r="N43" s="28"/>
-      <c r="O43" s="28"/>
-      <c r="P43" s="28"/>
-      <c r="Q43" s="28"/>
-      <c r="R43" s="28"/>
-      <c r="S43" s="28"/>
-      <c r="T43" s="28"/>
-      <c r="U43" s="28"/>
-      <c r="V43" s="28"/>
-      <c r="W43" s="28"/>
-      <c r="X43" s="28"/>
-      <c r="Y43" s="28"/>
-      <c r="Z43" s="28"/>
-      <c r="AA43" s="28"/>
-      <c r="AB43" s="28"/>
-      <c r="AC43" s="28"/>
+      <c r="A43" s="29" t="s">
+        <v>371</v>
+      </c>
+      <c r="B43" s="30"/>
+      <c r="C43" s="30"/>
+      <c r="D43" s="30"/>
+      <c r="E43" s="30"/>
+      <c r="F43" s="30"/>
+      <c r="G43" s="30"/>
+      <c r="H43" s="30"/>
+      <c r="I43" s="30"/>
+      <c r="J43" s="30"/>
+      <c r="K43" s="30"/>
+      <c r="L43" s="30"/>
+      <c r="M43" s="30"/>
+      <c r="N43" s="30"/>
+      <c r="O43" s="30"/>
+      <c r="P43" s="30"/>
+      <c r="Q43" s="30"/>
+      <c r="R43" s="30"/>
+      <c r="S43" s="30"/>
+      <c r="T43" s="30"/>
+      <c r="U43" s="30"/>
+      <c r="V43" s="30"/>
+      <c r="W43" s="30"/>
+      <c r="X43" s="30"/>
+      <c r="Y43" s="30"/>
+      <c r="Z43" s="30"/>
+      <c r="AA43" s="30"/>
+      <c r="AB43" s="30"/>
+      <c r="AC43" s="30"/>
     </row>
     <row r="44" ht="15.0" customHeight="1">
-      <c r="A44" s="29" t="s">
-        <v>371</v>
-      </c>
-      <c r="B44" s="31">
+      <c r="A44" s="31" t="s">
+        <v>372</v>
+      </c>
+      <c r="B44" s="33">
         <v>0.88</v>
       </c>
-      <c r="C44" s="31">
+      <c r="C44" s="33">
         <v>1.06</v>
       </c>
-      <c r="D44" s="31">
+      <c r="D44" s="33">
         <v>0.62</v>
       </c>
-      <c r="E44" s="31">
+      <c r="E44" s="33">
         <v>0.91</v>
       </c>
-      <c r="F44" s="31">
+      <c r="F44" s="33">
         <v>1.47</v>
       </c>
-      <c r="G44" s="31">
+      <c r="G44" s="33">
         <v>1.79</v>
       </c>
-      <c r="H44" s="31">
+      <c r="H44" s="33">
         <v>1.9</v>
       </c>
-      <c r="I44" s="31">
+      <c r="I44" s="33">
         <v>1.91</v>
       </c>
-      <c r="J44" s="31">
+      <c r="J44" s="33">
         <v>1.82</v>
       </c>
-      <c r="K44" s="31">
+      <c r="K44" s="33">
         <v>2.76</v>
       </c>
-      <c r="L44" s="31">
+      <c r="L44" s="33">
         <v>1.12</v>
       </c>
-      <c r="M44" s="31">
+      <c r="M44" s="33">
         <v>1.24</v>
       </c>
-      <c r="N44" s="31">
+      <c r="N44" s="33">
         <v>0.98</v>
       </c>
-      <c r="O44" s="31">
+      <c r="O44" s="33">
         <v>0.76</v>
       </c>
-      <c r="P44" s="31">
+      <c r="P44" s="33">
         <v>0.62</v>
       </c>
-      <c r="Q44" s="31">
+      <c r="Q44" s="33">
         <v>0.58</v>
       </c>
-      <c r="R44" s="31">
+      <c r="R44" s="33">
         <v>0.62</v>
       </c>
-      <c r="S44" s="31">
+      <c r="S44" s="33">
         <v>0.8</v>
       </c>
-      <c r="T44" s="31">
+      <c r="T44" s="33">
         <v>1.24</v>
       </c>
-      <c r="U44" s="31">
+      <c r="U44" s="33">
         <v>1.22</v>
       </c>
-      <c r="V44" s="31">
+      <c r="V44" s="33">
         <v>0.96</v>
       </c>
-      <c r="W44" s="31">
+      <c r="W44" s="33">
         <v>0.66</v>
       </c>
-      <c r="X44" s="31">
+      <c r="X44" s="33">
         <v>0.44</v>
       </c>
-      <c r="Y44" s="31">
+      <c r="Y44" s="33">
         <v>0.45</v>
       </c>
-      <c r="Z44" s="31">
+      <c r="Z44" s="33">
         <v>0.48</v>
       </c>
-      <c r="AA44" s="31">
+      <c r="AA44" s="33">
         <v>0.3</v>
       </c>
-      <c r="AB44" s="31">
+      <c r="AB44" s="33">
         <v>0.34</v>
       </c>
-      <c r="AC44" s="31">
+      <c r="AC44" s="33">
         <v>0.56</v>
       </c>
     </row>
     <row r="45" ht="15.0" customHeight="1">
-      <c r="A45" s="29" t="s">
-        <v>372</v>
-      </c>
-      <c r="B45" s="31">
+      <c r="A45" s="31" t="s">
+        <v>373</v>
+      </c>
+      <c r="B45" s="33">
         <v>0.97</v>
       </c>
-      <c r="C45" s="31">
+      <c r="C45" s="33">
         <v>1.13</v>
       </c>
-      <c r="D45" s="31">
+      <c r="D45" s="33">
         <v>1.27</v>
       </c>
-      <c r="E45" s="31">
+      <c r="E45" s="33">
         <v>1.52</v>
       </c>
-      <c r="F45" s="31">
+      <c r="F45" s="33">
         <v>1.76</v>
       </c>
-      <c r="G45" s="31">
+      <c r="G45" s="33">
         <v>1.98</v>
       </c>
-      <c r="H45" s="31">
+      <c r="H45" s="33">
         <v>1.92</v>
       </c>
-      <c r="I45" s="31">
+      <c r="I45" s="33">
         <v>1.83</v>
       </c>
-      <c r="J45" s="31">
+      <c r="J45" s="33">
         <v>1.68</v>
       </c>
-      <c r="K45" s="31">
+      <c r="K45" s="33">
         <v>1.48</v>
       </c>
-      <c r="L45" s="31">
+      <c r="L45" s="33">
         <v>0.97</v>
       </c>
-      <c r="M45" s="31">
+      <c r="M45" s="33">
         <v>0.86</v>
       </c>
-      <c r="N45" s="31">
+      <c r="N45" s="33">
         <v>0.72</v>
       </c>
-      <c r="O45" s="31">
+      <c r="O45" s="33">
         <v>0.69</v>
       </c>
-      <c r="P45" s="31">
+      <c r="P45" s="33">
         <v>0.8</v>
       </c>
-      <c r="Q45" s="31">
+      <c r="Q45" s="33">
         <v>0.91</v>
       </c>
-      <c r="R45" s="31">
+      <c r="R45" s="33">
         <v>0.98</v>
       </c>
-      <c r="S45" s="31">
+      <c r="S45" s="33">
         <v>0.99</v>
       </c>
-      <c r="T45" s="31">
+      <c r="T45" s="33">
         <v>0.95</v>
       </c>
-      <c r="U45" s="31">
+      <c r="U45" s="33">
         <v>0.78</v>
       </c>
-      <c r="V45" s="31">
+      <c r="V45" s="33">
         <v>0.61</v>
       </c>
-      <c r="W45" s="31">
+      <c r="W45" s="33">
         <v>0.47</v>
       </c>
-      <c r="X45" s="31">
+      <c r="X45" s="33">
         <v>0.41</v>
       </c>
-      <c r="Y45" s="31">
+      <c r="Y45" s="33">
         <v>0.42</v>
       </c>
-      <c r="Z45" s="32"/>
-      <c r="AA45" s="32"/>
-      <c r="AB45" s="32"/>
-      <c r="AC45" s="32"/>
+      <c r="Z45" s="34"/>
+      <c r="AA45" s="34"/>
+      <c r="AB45" s="34"/>
+      <c r="AC45" s="34"/>
     </row>
     <row r="46" ht="15.0" customHeight="1">
-      <c r="A46" s="27" t="s">
-        <v>373</v>
-      </c>
-      <c r="B46" s="28"/>
-      <c r="C46" s="28"/>
-      <c r="D46" s="28"/>
-      <c r="E46" s="28"/>
-      <c r="F46" s="28"/>
-      <c r="G46" s="28"/>
-      <c r="H46" s="28"/>
-      <c r="I46" s="28"/>
-      <c r="J46" s="28"/>
-      <c r="K46" s="28"/>
-      <c r="L46" s="28"/>
-      <c r="M46" s="28"/>
-      <c r="N46" s="28"/>
-      <c r="O46" s="28"/>
-      <c r="P46" s="28"/>
-      <c r="Q46" s="28"/>
-      <c r="R46" s="28"/>
-      <c r="S46" s="28"/>
-      <c r="T46" s="28"/>
-      <c r="U46" s="28"/>
-      <c r="V46" s="28"/>
-      <c r="W46" s="28"/>
-      <c r="X46" s="28"/>
-      <c r="Y46" s="28"/>
-      <c r="Z46" s="28"/>
-      <c r="AA46" s="28"/>
-      <c r="AB46" s="28"/>
-      <c r="AC46" s="28"/>
+      <c r="A46" s="29" t="s">
+        <v>374</v>
+      </c>
+      <c r="B46" s="30"/>
+      <c r="C46" s="30"/>
+      <c r="D46" s="30"/>
+      <c r="E46" s="30"/>
+      <c r="F46" s="30"/>
+      <c r="G46" s="30"/>
+      <c r="H46" s="30"/>
+      <c r="I46" s="30"/>
+      <c r="J46" s="30"/>
+      <c r="K46" s="30"/>
+      <c r="L46" s="30"/>
+      <c r="M46" s="30"/>
+      <c r="N46" s="30"/>
+      <c r="O46" s="30"/>
+      <c r="P46" s="30"/>
+      <c r="Q46" s="30"/>
+      <c r="R46" s="30"/>
+      <c r="S46" s="30"/>
+      <c r="T46" s="30"/>
+      <c r="U46" s="30"/>
+      <c r="V46" s="30"/>
+      <c r="W46" s="30"/>
+      <c r="X46" s="30"/>
+      <c r="Y46" s="30"/>
+      <c r="Z46" s="30"/>
+      <c r="AA46" s="30"/>
+      <c r="AB46" s="30"/>
+      <c r="AC46" s="30"/>
     </row>
     <row r="47" ht="15.0" customHeight="1">
-      <c r="A47" s="29" t="s">
-        <v>374</v>
-      </c>
-      <c r="B47" s="31">
+      <c r="A47" s="31" t="s">
+        <v>375</v>
+      </c>
+      <c r="B47" s="33">
         <v>3.79</v>
       </c>
-      <c r="C47" s="31">
+      <c r="C47" s="33">
         <v>19.32</v>
       </c>
-      <c r="D47" s="32"/>
-      <c r="E47" s="32"/>
-      <c r="F47" s="30">
+      <c r="D47" s="34"/>
+      <c r="E47" s="34"/>
+      <c r="F47" s="32">
         <v>592.39</v>
       </c>
-      <c r="G47" s="31">
+      <c r="G47" s="33">
         <v>47.8</v>
       </c>
-      <c r="H47" s="30">
+      <c r="H47" s="32">
         <v>162.58</v>
       </c>
-      <c r="I47" s="31">
+      <c r="I47" s="33">
         <v>92.0</v>
       </c>
-      <c r="J47" s="30">
+      <c r="J47" s="32">
         <v>192.58</v>
       </c>
-      <c r="K47" s="31">
+      <c r="K47" s="33">
         <v>45.71</v>
       </c>
-      <c r="L47" s="32"/>
-      <c r="M47" s="31">
+      <c r="L47" s="34"/>
+      <c r="M47" s="33">
         <v>60.52</v>
       </c>
-      <c r="N47" s="31">
+      <c r="N47" s="33">
         <v>38.97</v>
       </c>
-      <c r="O47" s="31">
+      <c r="O47" s="33">
         <v>8.68</v>
       </c>
-      <c r="P47" s="31">
+      <c r="P47" s="33">
         <v>7.75</v>
       </c>
-      <c r="Q47" s="32"/>
-      <c r="R47" s="32"/>
-      <c r="S47" s="32"/>
-      <c r="T47" s="31">
+      <c r="Q47" s="34"/>
+      <c r="R47" s="34"/>
+      <c r="S47" s="34"/>
+      <c r="T47" s="33">
         <v>65.08</v>
       </c>
-      <c r="U47" s="31">
+      <c r="U47" s="33">
         <v>47.44</v>
       </c>
-      <c r="V47" s="31">
+      <c r="V47" s="33">
         <v>12.93</v>
       </c>
-      <c r="W47" s="31">
+      <c r="W47" s="33">
         <v>13.85</v>
       </c>
-      <c r="X47" s="31">
+      <c r="X47" s="33">
         <v>4.98</v>
       </c>
-      <c r="Y47" s="31">
+      <c r="Y47" s="33">
         <v>3.7</v>
       </c>
-      <c r="Z47" s="31">
+      <c r="Z47" s="33">
         <v>15.75</v>
       </c>
-      <c r="AA47" s="31">
+      <c r="AA47" s="33">
         <v>4.97</v>
       </c>
-      <c r="AB47" s="32"/>
-      <c r="AC47" s="31">
+      <c r="AB47" s="34"/>
+      <c r="AC47" s="33">
         <v>34.26</v>
       </c>
     </row>
     <row r="48" ht="15.0" customHeight="1">
-      <c r="A48" s="29" t="s">
-        <v>375</v>
-      </c>
-      <c r="B48" s="31">
+      <c r="A48" s="31" t="s">
+        <v>376</v>
+      </c>
+      <c r="B48" s="33">
         <v>36.64</v>
       </c>
-      <c r="C48" s="30">
+      <c r="C48" s="32">
         <v>526.25</v>
       </c>
-      <c r="D48" s="32"/>
-      <c r="E48" s="30">
+      <c r="D48" s="34"/>
+      <c r="E48" s="32">
         <v>369.7</v>
       </c>
-      <c r="F48" s="30">
+      <c r="F48" s="32">
         <v>107.58</v>
       </c>
-      <c r="G48" s="31">
+      <c r="G48" s="33">
         <v>75.69</v>
       </c>
-      <c r="H48" s="30">
+      <c r="H48" s="32">
         <v>112.33</v>
       </c>
-      <c r="I48" s="31">
+      <c r="I48" s="33">
         <v>94.73</v>
       </c>
-      <c r="J48" s="31">
+      <c r="J48" s="33">
         <v>85.06</v>
       </c>
-      <c r="K48" s="31">
+      <c r="K48" s="33">
         <v>43.38</v>
       </c>
-      <c r="L48" s="31">
+      <c r="L48" s="33">
         <v>27.7</v>
       </c>
-      <c r="M48" s="31">
+      <c r="M48" s="33">
         <v>35.73</v>
       </c>
-      <c r="N48" s="31">
+      <c r="N48" s="33">
         <v>51.14</v>
       </c>
-      <c r="O48" s="32"/>
-      <c r="P48" s="32"/>
-      <c r="Q48" s="32"/>
-      <c r="R48" s="30">
+      <c r="O48" s="34"/>
+      <c r="P48" s="34"/>
+      <c r="Q48" s="34"/>
+      <c r="R48" s="32">
         <v>130.69</v>
       </c>
-      <c r="S48" s="31">
+      <c r="S48" s="33">
         <v>46.45</v>
       </c>
-      <c r="T48" s="31">
+      <c r="T48" s="33">
         <v>19.88</v>
       </c>
-      <c r="U48" s="31">
+      <c r="U48" s="33">
         <v>11.14</v>
       </c>
-      <c r="V48" s="31">
+      <c r="V48" s="33">
         <v>8.4</v>
       </c>
-      <c r="W48" s="31">
+      <c r="W48" s="33">
         <v>6.72</v>
       </c>
-      <c r="X48" s="31">
+      <c r="X48" s="33">
         <v>7.65</v>
       </c>
-      <c r="Y48" s="31">
+      <c r="Y48" s="33">
         <v>10.57</v>
       </c>
-      <c r="Z48" s="32"/>
-      <c r="AA48" s="32"/>
-      <c r="AB48" s="32"/>
-      <c r="AC48" s="32"/>
+      <c r="Z48" s="34"/>
+      <c r="AA48" s="34"/>
+      <c r="AB48" s="34"/>
+      <c r="AC48" s="34"/>
     </row>
     <row r="49" ht="15.0" customHeight="1">
-      <c r="A49" s="27" t="s">
-        <v>376</v>
-      </c>
-      <c r="B49" s="28"/>
-      <c r="C49" s="28"/>
-      <c r="D49" s="28"/>
-      <c r="E49" s="28"/>
-      <c r="F49" s="28"/>
-      <c r="G49" s="28"/>
-      <c r="H49" s="28"/>
-      <c r="I49" s="28"/>
-      <c r="J49" s="28"/>
-      <c r="K49" s="28"/>
-      <c r="L49" s="28"/>
-      <c r="M49" s="28"/>
-      <c r="N49" s="28"/>
-      <c r="O49" s="28"/>
-      <c r="P49" s="28"/>
-      <c r="Q49" s="28"/>
-      <c r="R49" s="28"/>
-      <c r="S49" s="28"/>
-      <c r="T49" s="28"/>
-      <c r="U49" s="28"/>
-      <c r="V49" s="28"/>
-      <c r="W49" s="28"/>
-      <c r="X49" s="28"/>
-      <c r="Y49" s="28"/>
-      <c r="Z49" s="28"/>
-      <c r="AA49" s="28"/>
-      <c r="AB49" s="28"/>
-      <c r="AC49" s="28"/>
+      <c r="A49" s="29" t="s">
+        <v>377</v>
+      </c>
+      <c r="B49" s="30"/>
+      <c r="C49" s="30"/>
+      <c r="D49" s="30"/>
+      <c r="E49" s="30"/>
+      <c r="F49" s="30"/>
+      <c r="G49" s="30"/>
+      <c r="H49" s="30"/>
+      <c r="I49" s="30"/>
+      <c r="J49" s="30"/>
+      <c r="K49" s="30"/>
+      <c r="L49" s="30"/>
+      <c r="M49" s="30"/>
+      <c r="N49" s="30"/>
+      <c r="O49" s="30"/>
+      <c r="P49" s="30"/>
+      <c r="Q49" s="30"/>
+      <c r="R49" s="30"/>
+      <c r="S49" s="30"/>
+      <c r="T49" s="30"/>
+      <c r="U49" s="30"/>
+      <c r="V49" s="30"/>
+      <c r="W49" s="30"/>
+      <c r="X49" s="30"/>
+      <c r="Y49" s="30"/>
+      <c r="Z49" s="30"/>
+      <c r="AA49" s="30"/>
+      <c r="AB49" s="30"/>
+      <c r="AC49" s="30"/>
     </row>
     <row r="50" ht="15.0" customHeight="1">
-      <c r="A50" s="29" t="s">
-        <v>377</v>
-      </c>
-      <c r="B50" s="31">
+      <c r="A50" s="31" t="s">
+        <v>378</v>
+      </c>
+      <c r="B50" s="33">
         <v>7.04</v>
       </c>
-      <c r="C50" s="31">
+      <c r="C50" s="33">
         <v>10.22</v>
       </c>
-      <c r="D50" s="31">
+      <c r="D50" s="33">
         <v>13.48</v>
       </c>
-      <c r="E50" s="31">
+      <c r="E50" s="33">
         <v>9.66</v>
       </c>
-      <c r="F50" s="31">
+      <c r="F50" s="33">
         <v>13.31</v>
       </c>
-      <c r="G50" s="31">
+      <c r="G50" s="33">
         <v>20.46</v>
       </c>
-      <c r="H50" s="31">
+      <c r="H50" s="33">
         <v>18.99</v>
       </c>
-      <c r="I50" s="31">
+      <c r="I50" s="33">
         <v>21.11</v>
       </c>
-      <c r="J50" s="31">
+      <c r="J50" s="33">
         <v>19.22</v>
       </c>
-      <c r="K50" s="31">
+      <c r="K50" s="33">
         <v>26.27</v>
       </c>
-      <c r="L50" s="31">
+      <c r="L50" s="33">
         <v>12.77</v>
       </c>
-      <c r="M50" s="31">
+      <c r="M50" s="33">
         <v>12.26</v>
       </c>
-      <c r="N50" s="31">
+      <c r="N50" s="33">
         <v>10.23</v>
       </c>
-      <c r="O50" s="31">
+      <c r="O50" s="33">
         <v>7.93</v>
       </c>
-      <c r="P50" s="31">
+      <c r="P50" s="33">
         <v>6.57</v>
       </c>
-      <c r="Q50" s="31">
+      <c r="Q50" s="33">
         <v>8.91</v>
       </c>
-      <c r="R50" s="31">
+      <c r="R50" s="33">
         <v>22.08</v>
       </c>
-      <c r="S50" s="31">
+      <c r="S50" s="33">
         <v>13.18</v>
       </c>
-      <c r="T50" s="31">
+      <c r="T50" s="33">
         <v>20.17</v>
       </c>
-      <c r="U50" s="31">
+      <c r="U50" s="33">
         <v>18.84</v>
       </c>
-      <c r="V50" s="31">
+      <c r="V50" s="33">
         <v>13.83</v>
       </c>
-      <c r="W50" s="31">
+      <c r="W50" s="33">
         <v>6.75</v>
       </c>
-      <c r="X50" s="31">
+      <c r="X50" s="33">
         <v>4.54</v>
       </c>
-      <c r="Y50" s="31">
+      <c r="Y50" s="33">
         <v>4.75</v>
       </c>
-      <c r="Z50" s="31">
+      <c r="Z50" s="33">
         <v>4.58</v>
       </c>
-      <c r="AA50" s="31">
+      <c r="AA50" s="33">
         <v>2.89</v>
       </c>
-      <c r="AB50" s="31">
+      <c r="AB50" s="33">
         <v>4.46</v>
       </c>
-      <c r="AC50" s="31">
+      <c r="AC50" s="33">
         <v>5.56</v>
       </c>
     </row>
     <row r="51" ht="15.0" customHeight="1">
-      <c r="A51" s="29" t="s">
-        <v>378</v>
-      </c>
-      <c r="B51" s="31">
+      <c r="A51" s="31" t="s">
+        <v>379</v>
+      </c>
+      <c r="B51" s="33">
         <v>10.67</v>
       </c>
-      <c r="C51" s="31">
+      <c r="C51" s="33">
         <v>13.14</v>
       </c>
-      <c r="D51" s="31">
+      <c r="D51" s="33">
         <v>14.67</v>
       </c>
-      <c r="E51" s="31">
+      <c r="E51" s="33">
         <v>15.73</v>
       </c>
-      <c r="F51" s="31">
+      <c r="F51" s="33">
         <v>18.1</v>
       </c>
-      <c r="G51" s="31">
+      <c r="G51" s="33">
         <v>20.86</v>
       </c>
-      <c r="H51" s="31">
+      <c r="H51" s="33">
         <v>19.99</v>
       </c>
-      <c r="I51" s="31">
+      <c r="I51" s="33">
         <v>19.24</v>
       </c>
-      <c r="J51" s="31">
+      <c r="J51" s="33">
         <v>17.31</v>
       </c>
-      <c r="K51" s="31">
+      <c r="K51" s="33">
         <v>15.2</v>
       </c>
-      <c r="L51" s="31">
+      <c r="L51" s="33">
         <v>10.18</v>
       </c>
-      <c r="M51" s="31">
+      <c r="M51" s="33">
         <v>9.36</v>
       </c>
-      <c r="N51" s="31">
+      <c r="N51" s="33">
         <v>9.25</v>
       </c>
-      <c r="O51" s="31">
+      <c r="O51" s="33">
         <v>9.75</v>
       </c>
-      <c r="P51" s="31">
+      <c r="P51" s="33">
         <v>12.61</v>
       </c>
-      <c r="Q51" s="31">
+      <c r="Q51" s="33">
         <v>16.0</v>
       </c>
-      <c r="R51" s="31">
+      <c r="R51" s="33">
         <v>16.99</v>
       </c>
-      <c r="S51" s="31">
+      <c r="S51" s="33">
         <v>14.4</v>
       </c>
-      <c r="T51" s="31">
+      <c r="T51" s="33">
         <v>12.54</v>
       </c>
-      <c r="U51" s="31">
+      <c r="U51" s="33">
         <v>9.31</v>
       </c>
-      <c r="V51" s="31">
+      <c r="V51" s="33">
         <v>6.57</v>
       </c>
-      <c r="W51" s="31">
+      <c r="W51" s="33">
         <v>4.68</v>
       </c>
-      <c r="X51" s="31">
+      <c r="X51" s="33">
         <v>4.23</v>
       </c>
-      <c r="Y51" s="31">
+      <c r="Y51" s="33">
         <v>4.37</v>
       </c>
-      <c r="Z51" s="32"/>
-      <c r="AA51" s="32"/>
-      <c r="AB51" s="32"/>
-      <c r="AC51" s="32"/>
+      <c r="Z51" s="34"/>
+      <c r="AA51" s="34"/>
+      <c r="AB51" s="34"/>
+      <c r="AC51" s="34"/>
     </row>
     <row r="52" ht="15.0" customHeight="1">
-      <c r="A52" s="27" t="s">
-        <v>379</v>
-      </c>
-      <c r="B52" s="28"/>
-      <c r="C52" s="28"/>
-      <c r="D52" s="28"/>
-      <c r="E52" s="28"/>
-      <c r="F52" s="28"/>
-      <c r="G52" s="28"/>
-      <c r="H52" s="28"/>
-      <c r="I52" s="28"/>
-      <c r="J52" s="28"/>
-      <c r="K52" s="28"/>
-      <c r="L52" s="28"/>
-      <c r="M52" s="28"/>
-      <c r="N52" s="28"/>
-      <c r="O52" s="28"/>
-      <c r="P52" s="28"/>
-      <c r="Q52" s="28"/>
-      <c r="R52" s="28"/>
-      <c r="S52" s="28"/>
-      <c r="T52" s="28"/>
-      <c r="U52" s="28"/>
-      <c r="V52" s="28"/>
-      <c r="W52" s="28"/>
-      <c r="X52" s="28"/>
-      <c r="Y52" s="28"/>
-      <c r="Z52" s="28"/>
-      <c r="AA52" s="28"/>
-      <c r="AB52" s="28"/>
-      <c r="AC52" s="28"/>
+      <c r="A52" s="29" t="s">
+        <v>380</v>
+      </c>
+      <c r="B52" s="30"/>
+      <c r="C52" s="30"/>
+      <c r="D52" s="30"/>
+      <c r="E52" s="30"/>
+      <c r="F52" s="30"/>
+      <c r="G52" s="30"/>
+      <c r="H52" s="30"/>
+      <c r="I52" s="30"/>
+      <c r="J52" s="30"/>
+      <c r="K52" s="30"/>
+      <c r="L52" s="30"/>
+      <c r="M52" s="30"/>
+      <c r="N52" s="30"/>
+      <c r="O52" s="30"/>
+      <c r="P52" s="30"/>
+      <c r="Q52" s="30"/>
+      <c r="R52" s="30"/>
+      <c r="S52" s="30"/>
+      <c r="T52" s="30"/>
+      <c r="U52" s="30"/>
+      <c r="V52" s="30"/>
+      <c r="W52" s="30"/>
+      <c r="X52" s="30"/>
+      <c r="Y52" s="30"/>
+      <c r="Z52" s="30"/>
+      <c r="AA52" s="30"/>
+      <c r="AB52" s="30"/>
+      <c r="AC52" s="30"/>
     </row>
     <row r="53" ht="15.0" customHeight="1">
-      <c r="A53" s="29" t="s">
-        <v>380</v>
-      </c>
-      <c r="B53" s="31">
+      <c r="A53" s="31" t="s">
+        <v>381</v>
+      </c>
+      <c r="B53" s="33">
         <v>18.28</v>
       </c>
-      <c r="C53" s="32"/>
-      <c r="D53" s="32"/>
-      <c r="E53" s="31">
+      <c r="C53" s="34"/>
+      <c r="D53" s="34"/>
+      <c r="E53" s="33">
         <v>16.74</v>
       </c>
-      <c r="F53" s="31">
+      <c r="F53" s="33">
         <v>25.79</v>
       </c>
-      <c r="G53" s="31">
+      <c r="G53" s="33">
         <v>52.16</v>
       </c>
-      <c r="H53" s="31">
+      <c r="H53" s="33">
         <v>27.47</v>
       </c>
-      <c r="I53" s="31">
+      <c r="I53" s="33">
         <v>26.45</v>
       </c>
-      <c r="J53" s="31">
+      <c r="J53" s="33">
         <v>24.78</v>
       </c>
-      <c r="K53" s="31">
+      <c r="K53" s="33">
         <v>31.47</v>
       </c>
-      <c r="L53" s="31">
+      <c r="L53" s="33">
         <v>17.81</v>
       </c>
-      <c r="M53" s="31">
+      <c r="M53" s="33">
         <v>15.95</v>
       </c>
-      <c r="N53" s="31">
+      <c r="N53" s="33">
         <v>14.37</v>
       </c>
-      <c r="O53" s="31">
+      <c r="O53" s="33">
         <v>10.64</v>
       </c>
-      <c r="P53" s="31">
+      <c r="P53" s="33">
         <v>8.97</v>
       </c>
-      <c r="Q53" s="31">
+      <c r="Q53" s="33">
         <v>12.61</v>
       </c>
-      <c r="R53" s="31">
+      <c r="R53" s="33">
         <v>92.34</v>
       </c>
-      <c r="S53" s="31">
+      <c r="S53" s="33">
         <v>13.1</v>
       </c>
-      <c r="T53" s="31">
+      <c r="T53" s="33">
         <v>18.29</v>
       </c>
-      <c r="U53" s="31">
+      <c r="U53" s="33">
         <v>18.08</v>
       </c>
-      <c r="V53" s="31">
+      <c r="V53" s="33">
         <v>12.65</v>
       </c>
-      <c r="W53" s="31">
+      <c r="W53" s="33">
         <v>10.86</v>
       </c>
-      <c r="X53" s="31">
+      <c r="X53" s="33">
         <v>8.06</v>
       </c>
-      <c r="Y53" s="31">
+      <c r="Y53" s="33">
         <v>8.37</v>
       </c>
-      <c r="Z53" s="31">
+      <c r="Z53" s="33">
         <v>7.35</v>
       </c>
-      <c r="AA53" s="31">
+      <c r="AA53" s="33">
         <v>4.99</v>
       </c>
-      <c r="AB53" s="31">
+      <c r="AB53" s="33">
         <v>13.61</v>
       </c>
-      <c r="AC53" s="31">
+      <c r="AC53" s="33">
         <v>9.08</v>
       </c>
     </row>
     <row r="54" ht="15.0" customHeight="1">
-      <c r="A54" s="29" t="s">
-        <v>381</v>
-      </c>
-      <c r="B54" s="31">
+      <c r="A54" s="31" t="s">
+        <v>382</v>
+      </c>
+      <c r="B54" s="33">
         <v>33.96</v>
       </c>
-      <c r="C54" s="31">
+      <c r="C54" s="33">
         <v>41.68</v>
       </c>
-      <c r="D54" s="31">
+      <c r="D54" s="33">
         <v>30.99</v>
       </c>
-      <c r="E54" s="31">
+      <c r="E54" s="33">
         <v>26.89</v>
       </c>
-      <c r="F54" s="31">
+      <c r="F54" s="33">
         <v>29.46</v>
       </c>
-      <c r="G54" s="31">
+      <c r="G54" s="33">
         <v>30.73</v>
       </c>
-      <c r="H54" s="31">
+      <c r="H54" s="33">
         <v>26.34</v>
       </c>
-      <c r="I54" s="31">
+      <c r="I54" s="33">
         <v>24.53</v>
       </c>
-      <c r="J54" s="31">
+      <c r="J54" s="33">
         <v>22.51</v>
       </c>
-      <c r="K54" s="31">
+      <c r="K54" s="33">
         <v>19.91</v>
       </c>
-      <c r="L54" s="31">
+      <c r="L54" s="33">
         <v>13.85</v>
       </c>
-      <c r="M54" s="31">
+      <c r="M54" s="33">
         <v>12.71</v>
       </c>
-      <c r="N54" s="31">
+      <c r="N54" s="33">
         <v>13.31</v>
       </c>
-      <c r="O54" s="31">
+      <c r="O54" s="33">
         <v>12.95</v>
       </c>
-      <c r="P54" s="31">
+      <c r="P54" s="33">
         <v>15.15</v>
       </c>
-      <c r="Q54" s="31">
+      <c r="Q54" s="33">
         <v>17.53</v>
       </c>
-      <c r="R54" s="31">
+      <c r="R54" s="33">
         <v>17.1</v>
       </c>
-      <c r="S54" s="31">
+      <c r="S54" s="33">
         <v>14.93</v>
       </c>
-      <c r="T54" s="31">
+      <c r="T54" s="33">
         <v>14.4</v>
       </c>
-      <c r="U54" s="31">
+      <c r="U54" s="33">
         <v>12.29</v>
       </c>
-      <c r="V54" s="31">
+      <c r="V54" s="33">
         <v>9.7</v>
       </c>
-      <c r="W54" s="31">
+      <c r="W54" s="33">
         <v>7.9</v>
       </c>
-      <c r="X54" s="31">
+      <c r="X54" s="33">
         <v>7.65</v>
       </c>
-      <c r="Y54" s="31">
+      <c r="Y54" s="33">
         <v>7.81</v>
       </c>
-      <c r="Z54" s="32"/>
-      <c r="AA54" s="32"/>
-      <c r="AB54" s="32"/>
-      <c r="AC54" s="32"/>
+      <c r="Z54" s="34"/>
+      <c r="AA54" s="34"/>
+      <c r="AB54" s="34"/>
+      <c r="AC54" s="34"/>
     </row>
     <row r="55" ht="15.0" customHeight="1">
-      <c r="A55" s="27" t="s">
-        <v>382</v>
-      </c>
-      <c r="B55" s="28"/>
-      <c r="C55" s="28"/>
-      <c r="D55" s="28"/>
-      <c r="E55" s="28"/>
-      <c r="F55" s="28"/>
-      <c r="G55" s="28"/>
-      <c r="H55" s="28"/>
-      <c r="I55" s="28"/>
-      <c r="J55" s="28"/>
-      <c r="K55" s="28"/>
-      <c r="L55" s="28"/>
-      <c r="M55" s="28"/>
-      <c r="N55" s="28"/>
-      <c r="O55" s="28"/>
-      <c r="P55" s="28"/>
-      <c r="Q55" s="28"/>
-      <c r="R55" s="28"/>
-      <c r="S55" s="28"/>
-      <c r="T55" s="28"/>
-      <c r="U55" s="28"/>
-      <c r="V55" s="28"/>
-      <c r="W55" s="28"/>
-      <c r="X55" s="28"/>
-      <c r="Y55" s="28"/>
-      <c r="Z55" s="28"/>
-      <c r="AA55" s="28"/>
-      <c r="AB55" s="28"/>
-      <c r="AC55" s="28"/>
+      <c r="A55" s="29" t="s">
+        <v>383</v>
+      </c>
+      <c r="B55" s="30"/>
+      <c r="C55" s="30"/>
+      <c r="D55" s="30"/>
+      <c r="E55" s="30"/>
+      <c r="F55" s="30"/>
+      <c r="G55" s="30"/>
+      <c r="H55" s="30"/>
+      <c r="I55" s="30"/>
+      <c r="J55" s="30"/>
+      <c r="K55" s="30"/>
+      <c r="L55" s="30"/>
+      <c r="M55" s="30"/>
+      <c r="N55" s="30"/>
+      <c r="O55" s="30"/>
+      <c r="P55" s="30"/>
+      <c r="Q55" s="30"/>
+      <c r="R55" s="30"/>
+      <c r="S55" s="30"/>
+      <c r="T55" s="30"/>
+      <c r="U55" s="30"/>
+      <c r="V55" s="30"/>
+      <c r="W55" s="30"/>
+      <c r="X55" s="30"/>
+      <c r="Y55" s="30"/>
+      <c r="Z55" s="30"/>
+      <c r="AA55" s="30"/>
+      <c r="AB55" s="30"/>
+      <c r="AC55" s="30"/>
     </row>
     <row r="56" ht="15.0" customHeight="1">
-      <c r="A56" s="29" t="s">
-        <v>383</v>
-      </c>
-      <c r="B56" s="31">
+      <c r="A56" s="31" t="s">
+        <v>384</v>
+      </c>
+      <c r="B56" s="33">
         <v>18.28</v>
       </c>
-      <c r="C56" s="32"/>
-      <c r="D56" s="32"/>
-      <c r="E56" s="31">
+      <c r="C56" s="34"/>
+      <c r="D56" s="34"/>
+      <c r="E56" s="33">
         <v>16.64</v>
       </c>
-      <c r="F56" s="31">
+      <c r="F56" s="33">
         <v>25.21</v>
       </c>
-      <c r="G56" s="31">
+      <c r="G56" s="33">
         <v>51.0</v>
       </c>
-      <c r="H56" s="31">
+      <c r="H56" s="33">
         <v>25.27</v>
       </c>
-      <c r="I56" s="31">
+      <c r="I56" s="33">
         <v>23.97</v>
       </c>
-      <c r="J56" s="31">
+      <c r="J56" s="33">
         <v>24.46</v>
       </c>
-      <c r="K56" s="31">
+      <c r="K56" s="33">
         <v>30.39</v>
       </c>
-      <c r="L56" s="31">
+      <c r="L56" s="33">
         <v>16.61</v>
       </c>
-      <c r="M56" s="31">
+      <c r="M56" s="33">
         <v>15.65</v>
       </c>
-      <c r="N56" s="31">
+      <c r="N56" s="33">
         <v>13.74</v>
       </c>
-      <c r="O56" s="31">
+      <c r="O56" s="33">
         <v>10.19</v>
       </c>
-      <c r="P56" s="31">
+      <c r="P56" s="33">
         <v>8.76</v>
       </c>
-      <c r="Q56" s="31">
+      <c r="Q56" s="33">
         <v>10.64</v>
       </c>
-      <c r="R56" s="31">
+      <c r="R56" s="33">
         <v>23.93</v>
       </c>
-      <c r="S56" s="31">
+      <c r="S56" s="33">
         <v>18.53</v>
       </c>
-      <c r="T56" s="31">
+      <c r="T56" s="33">
         <v>26.09</v>
       </c>
-      <c r="U56" s="31">
+      <c r="U56" s="33">
         <v>27.4</v>
       </c>
-      <c r="V56" s="31">
+      <c r="V56" s="33">
         <v>19.69</v>
       </c>
-      <c r="W56" s="31">
+      <c r="W56" s="33">
         <v>10.86</v>
       </c>
-      <c r="X56" s="31">
+      <c r="X56" s="33">
         <v>8.06</v>
       </c>
-      <c r="Y56" s="31">
+      <c r="Y56" s="33">
         <v>8.37</v>
       </c>
-      <c r="Z56" s="31">
+      <c r="Z56" s="33">
         <v>7.35</v>
       </c>
-      <c r="AA56" s="31">
+      <c r="AA56" s="33">
         <v>4.99</v>
       </c>
-      <c r="AB56" s="31">
+      <c r="AB56" s="33">
         <v>13.61</v>
       </c>
-      <c r="AC56" s="31">
+      <c r="AC56" s="33">
         <v>9.08</v>
       </c>
     </row>
     <row r="57" ht="15.0" customHeight="1">
-      <c r="A57" s="29" t="s">
-        <v>384</v>
-      </c>
-      <c r="B57" s="31">
+      <c r="A57" s="31" t="s">
+        <v>385</v>
+      </c>
+      <c r="B57" s="33">
         <v>2.42</v>
       </c>
-      <c r="C57" s="31">
+      <c r="C57" s="33">
         <v>2.94</v>
       </c>
-      <c r="D57" s="31">
+      <c r="D57" s="33">
         <v>3.43</v>
       </c>
-      <c r="E57" s="31">
+      <c r="E57" s="33">
         <v>3.99</v>
       </c>
-      <c r="F57" s="31">
+      <c r="F57" s="33">
         <v>4.34</v>
       </c>
-      <c r="G57" s="31">
+      <c r="G57" s="33">
         <v>4.67</v>
       </c>
-      <c r="H57" s="31">
+      <c r="H57" s="33">
         <v>4.28</v>
       </c>
-      <c r="I57" s="31">
+      <c r="I57" s="33">
         <v>3.79</v>
       </c>
-      <c r="J57" s="31">
+      <c r="J57" s="33">
         <v>3.21</v>
       </c>
-      <c r="K57" s="31">
+      <c r="K57" s="33">
         <v>2.65</v>
       </c>
-      <c r="L57" s="31">
+      <c r="L57" s="33">
         <v>1.69</v>
       </c>
-      <c r="M57" s="31">
+      <c r="M57" s="33">
         <v>1.47</v>
       </c>
-      <c r="N57" s="31">
+      <c r="N57" s="33">
         <v>1.26</v>
       </c>
-      <c r="O57" s="31">
+      <c r="O57" s="33">
         <v>1.27</v>
       </c>
-      <c r="P57" s="31">
+      <c r="P57" s="33">
         <v>1.59</v>
       </c>
-      <c r="Q57" s="31">
+      <c r="Q57" s="33">
         <v>1.93</v>
       </c>
-      <c r="R57" s="31">
+      <c r="R57" s="33">
         <v>2.18</v>
       </c>
-      <c r="S57" s="31">
+      <c r="S57" s="33">
         <v>2.3</v>
       </c>
-      <c r="T57" s="31">
+      <c r="T57" s="33">
         <v>2.22</v>
       </c>
-      <c r="U57" s="31">
+      <c r="U57" s="33">
         <v>1.84</v>
       </c>
-      <c r="V57" s="31">
+      <c r="V57" s="33">
         <v>1.52</v>
       </c>
-      <c r="W57" s="31">
+      <c r="W57" s="33">
         <v>1.28</v>
       </c>
-      <c r="X57" s="31">
+      <c r="X57" s="33">
         <v>1.22</v>
       </c>
-      <c r="Y57" s="31">
+      <c r="Y57" s="33">
         <v>1.33</v>
       </c>
-      <c r="Z57" s="32"/>
-      <c r="AA57" s="32"/>
-      <c r="AB57" s="32"/>
-      <c r="AC57" s="32"/>
+      <c r="Z57" s="34"/>
+      <c r="AA57" s="34"/>
+      <c r="AB57" s="34"/>
+      <c r="AC57" s="34"/>
     </row>
     <row r="58" ht="15.0" customHeight="1">
-      <c r="A58" s="27" t="s">
-        <v>385</v>
-      </c>
-      <c r="B58" s="28"/>
-      <c r="C58" s="28"/>
-      <c r="D58" s="28"/>
-      <c r="E58" s="28"/>
-      <c r="F58" s="28"/>
-      <c r="G58" s="28"/>
-      <c r="H58" s="28"/>
-      <c r="I58" s="28"/>
-      <c r="J58" s="28"/>
-      <c r="K58" s="28"/>
-      <c r="L58" s="28"/>
-      <c r="M58" s="28"/>
-      <c r="N58" s="28"/>
-      <c r="O58" s="28"/>
-      <c r="P58" s="28"/>
-      <c r="Q58" s="28"/>
-      <c r="R58" s="28"/>
-      <c r="S58" s="28"/>
-      <c r="T58" s="28"/>
-      <c r="U58" s="28"/>
-      <c r="V58" s="28"/>
-      <c r="W58" s="28"/>
-      <c r="X58" s="28"/>
-      <c r="Y58" s="28"/>
-      <c r="Z58" s="28"/>
-      <c r="AA58" s="28"/>
-      <c r="AB58" s="28"/>
-      <c r="AC58" s="28"/>
+      <c r="A58" s="29" t="s">
+        <v>386</v>
+      </c>
+      <c r="B58" s="30"/>
+      <c r="C58" s="30"/>
+      <c r="D58" s="30"/>
+      <c r="E58" s="30"/>
+      <c r="F58" s="30"/>
+      <c r="G58" s="30"/>
+      <c r="H58" s="30"/>
+      <c r="I58" s="30"/>
+      <c r="J58" s="30"/>
+      <c r="K58" s="30"/>
+      <c r="L58" s="30"/>
+      <c r="M58" s="30"/>
+      <c r="N58" s="30"/>
+      <c r="O58" s="30"/>
+      <c r="P58" s="30"/>
+      <c r="Q58" s="30"/>
+      <c r="R58" s="30"/>
+      <c r="S58" s="30"/>
+      <c r="T58" s="30"/>
+      <c r="U58" s="30"/>
+      <c r="V58" s="30"/>
+      <c r="W58" s="30"/>
+      <c r="X58" s="30"/>
+      <c r="Y58" s="30"/>
+      <c r="Z58" s="30"/>
+      <c r="AA58" s="30"/>
+      <c r="AB58" s="30"/>
+      <c r="AC58" s="30"/>
     </row>
     <row r="59" ht="15.0" customHeight="1">
-      <c r="A59" s="29" t="s">
-        <v>386</v>
-      </c>
-      <c r="B59" s="31">
+      <c r="A59" s="31" t="s">
+        <v>387</v>
+      </c>
+      <c r="B59" s="33">
         <v>0.07</v>
       </c>
-      <c r="C59" s="32"/>
-      <c r="D59" s="32"/>
-      <c r="E59" s="31">
+      <c r="C59" s="34"/>
+      <c r="D59" s="34"/>
+      <c r="E59" s="33">
         <v>0.64</v>
       </c>
-      <c r="F59" s="31">
+      <c r="F59" s="33">
         <v>0.3</v>
       </c>
-      <c r="G59" s="35">
+      <c r="G59" s="37">
         <v>-1.07</v>
       </c>
-      <c r="H59" s="31">
+      <c r="H59" s="33">
         <v>2.15</v>
       </c>
-      <c r="I59" s="31">
+      <c r="I59" s="33">
         <v>1.33</v>
       </c>
-      <c r="J59" s="31">
+      <c r="J59" s="33">
         <v>4.27</v>
       </c>
-      <c r="K59" s="31">
+      <c r="K59" s="33">
         <v>0.51</v>
       </c>
-      <c r="L59" s="35">
+      <c r="L59" s="37">
         <v>-4.83</v>
       </c>
-      <c r="M59" s="31">
+      <c r="M59" s="33">
         <v>0.73</v>
       </c>
-      <c r="N59" s="31">
+      <c r="N59" s="33">
         <v>10.34</v>
       </c>
-      <c r="O59" s="31">
+      <c r="O59" s="33">
         <v>1.98</v>
       </c>
-      <c r="P59" s="31">
+      <c r="P59" s="33">
         <v>0.14</v>
       </c>
-      <c r="Q59" s="31">
+      <c r="Q59" s="33">
         <v>0.02</v>
       </c>
-      <c r="R59" s="35">
+      <c r="R59" s="37">
         <v>-1.0</v>
       </c>
-      <c r="S59" s="35">
+      <c r="S59" s="37">
         <v>-1.38</v>
       </c>
-      <c r="T59" s="31">
+      <c r="T59" s="33">
         <v>1.09</v>
       </c>
-      <c r="U59" s="35">
+      <c r="U59" s="37">
         <v>-9.06</v>
       </c>
-      <c r="V59" s="31">
+      <c r="V59" s="33">
         <v>0.27</v>
       </c>
-      <c r="W59" s="31">
+      <c r="W59" s="33">
         <v>1.01</v>
       </c>
-      <c r="X59" s="35">
+      <c r="X59" s="37">
         <v>-2.74</v>
       </c>
-      <c r="Y59" s="35">
+      <c r="Y59" s="37">
         <v>-0.38</v>
       </c>
-      <c r="Z59" s="31">
+      <c r="Z59" s="33">
         <v>0.34</v>
       </c>
-      <c r="AA59" s="31">
+      <c r="AA59" s="33">
         <v>0.02</v>
       </c>
-      <c r="AB59" s="35">
+      <c r="AB59" s="37">
         <v>-0.25</v>
       </c>
-      <c r="AC59" s="32"/>
+      <c r="AC59" s="34"/>
     </row>
     <row r="60" ht="15.0" customHeight="1">
-      <c r="A60" s="29" t="s">
-        <v>387</v>
-      </c>
-      <c r="B60" s="36">
+      <c r="A60" s="31" t="s">
+        <v>388</v>
+      </c>
+      <c r="B60" s="38">
         <v>-222.78</v>
       </c>
-      <c r="C60" s="32"/>
-      <c r="D60" s="32"/>
-      <c r="E60" s="31">
+      <c r="C60" s="34"/>
+      <c r="D60" s="34"/>
+      <c r="E60" s="33">
         <v>2.71</v>
       </c>
-      <c r="F60" s="31">
+      <c r="F60" s="33">
         <v>4.78</v>
       </c>
-      <c r="G60" s="31">
+      <c r="G60" s="33">
         <v>8.94</v>
       </c>
-      <c r="H60" s="31">
+      <c r="H60" s="33">
         <v>1.51</v>
       </c>
-      <c r="I60" s="31">
+      <c r="I60" s="33">
         <v>1.27</v>
       </c>
-      <c r="J60" s="31">
+      <c r="J60" s="33">
         <v>1.47</v>
       </c>
-      <c r="K60" s="31">
+      <c r="K60" s="33">
         <v>1.31</v>
       </c>
-      <c r="L60" s="31">
+      <c r="L60" s="33">
         <v>0.88</v>
       </c>
-      <c r="M60" s="31">
+      <c r="M60" s="33">
         <v>0.17</v>
       </c>
-      <c r="N60" s="31">
+      <c r="N60" s="33">
         <v>11.72</v>
       </c>
-      <c r="O60" s="35">
+      <c r="O60" s="37">
         <v>-11.39</v>
       </c>
-      <c r="P60" s="31">
+      <c r="P60" s="33">
         <v>16.41</v>
       </c>
-      <c r="Q60" s="35">
+      <c r="Q60" s="37">
         <v>-1.92</v>
       </c>
-      <c r="R60" s="35">
+      <c r="R60" s="37">
         <v>-0.5</v>
       </c>
-      <c r="S60" s="31">
+      <c r="S60" s="33">
         <v>1.35</v>
       </c>
-      <c r="T60" s="31">
+      <c r="T60" s="33">
         <v>1.14</v>
       </c>
-      <c r="U60" s="31">
+      <c r="U60" s="33">
         <v>3.24</v>
       </c>
-      <c r="V60" s="31">
+      <c r="V60" s="33">
         <v>1.16</v>
       </c>
-      <c r="W60" s="31">
+      <c r="W60" s="33">
         <v>0.31</v>
       </c>
-      <c r="X60" s="31">
+      <c r="X60" s="33">
         <v>1.62</v>
       </c>
-      <c r="Y60" s="32"/>
-      <c r="Z60" s="32"/>
-      <c r="AA60" s="32"/>
-      <c r="AB60" s="32"/>
-      <c r="AC60" s="32"/>
+      <c r="Y60" s="34"/>
+      <c r="Z60" s="34"/>
+      <c r="AA60" s="34"/>
+      <c r="AB60" s="34"/>
+      <c r="AC60" s="34"/>
     </row>
     <row r="61" ht="15.0" customHeight="1">
-      <c r="A61" s="27" t="s">
-        <v>388</v>
-      </c>
-      <c r="B61" s="28"/>
-      <c r="C61" s="28"/>
-      <c r="D61" s="28"/>
-      <c r="E61" s="28"/>
-      <c r="F61" s="28"/>
-      <c r="G61" s="28"/>
-      <c r="H61" s="28"/>
-      <c r="I61" s="28"/>
-      <c r="J61" s="28"/>
-      <c r="K61" s="28"/>
-      <c r="L61" s="28"/>
-      <c r="M61" s="28"/>
-      <c r="N61" s="28"/>
-      <c r="O61" s="28"/>
-      <c r="P61" s="28"/>
-      <c r="Q61" s="28"/>
-      <c r="R61" s="28"/>
-      <c r="S61" s="28"/>
-      <c r="T61" s="28"/>
-      <c r="U61" s="28"/>
-      <c r="V61" s="28"/>
-      <c r="W61" s="28"/>
-      <c r="X61" s="28"/>
-      <c r="Y61" s="28"/>
-      <c r="Z61" s="28"/>
-      <c r="AA61" s="28"/>
-      <c r="AB61" s="28"/>
-      <c r="AC61" s="28"/>
+      <c r="A61" s="29" t="s">
+        <v>389</v>
+      </c>
+      <c r="B61" s="30"/>
+      <c r="C61" s="30"/>
+      <c r="D61" s="30"/>
+      <c r="E61" s="30"/>
+      <c r="F61" s="30"/>
+      <c r="G61" s="30"/>
+      <c r="H61" s="30"/>
+      <c r="I61" s="30"/>
+      <c r="J61" s="30"/>
+      <c r="K61" s="30"/>
+      <c r="L61" s="30"/>
+      <c r="M61" s="30"/>
+      <c r="N61" s="30"/>
+      <c r="O61" s="30"/>
+      <c r="P61" s="30"/>
+      <c r="Q61" s="30"/>
+      <c r="R61" s="30"/>
+      <c r="S61" s="30"/>
+      <c r="T61" s="30"/>
+      <c r="U61" s="30"/>
+      <c r="V61" s="30"/>
+      <c r="W61" s="30"/>
+      <c r="X61" s="30"/>
+      <c r="Y61" s="30"/>
+      <c r="Z61" s="30"/>
+      <c r="AA61" s="30"/>
+      <c r="AB61" s="30"/>
+      <c r="AC61" s="30"/>
     </row>
     <row r="62" ht="15.0" customHeight="1">
-      <c r="A62" s="29" t="s">
-        <v>389</v>
-      </c>
-      <c r="B62" s="31">
+      <c r="A62" s="31" t="s">
+        <v>390</v>
+      </c>
+      <c r="B62" s="33">
         <v>1.5</v>
       </c>
-      <c r="C62" s="31">
+      <c r="C62" s="33">
         <v>1.81</v>
       </c>
-      <c r="D62" s="31">
+      <c r="D62" s="33">
         <v>1.01</v>
       </c>
-      <c r="E62" s="31">
+      <c r="E62" s="33">
         <v>1.2</v>
       </c>
-      <c r="F62" s="31">
+      <c r="F62" s="33">
         <v>1.77</v>
       </c>
-      <c r="G62" s="31">
+      <c r="G62" s="33">
         <v>2.09</v>
       </c>
-      <c r="H62" s="31">
+      <c r="H62" s="33">
         <v>2.09</v>
       </c>
-      <c r="I62" s="31">
+      <c r="I62" s="33">
         <v>2.0</v>
       </c>
-      <c r="J62" s="31">
+      <c r="J62" s="33">
         <v>1.91</v>
       </c>
-      <c r="K62" s="31">
+      <c r="K62" s="33">
         <v>2.74</v>
       </c>
-      <c r="L62" s="31">
+      <c r="L62" s="33">
         <v>1.22</v>
       </c>
-      <c r="M62" s="31">
+      <c r="M62" s="33">
         <v>1.29</v>
       </c>
-      <c r="N62" s="31">
+      <c r="N62" s="33">
         <v>1.05</v>
       </c>
-      <c r="O62" s="31">
+      <c r="O62" s="33">
         <v>0.85</v>
       </c>
-      <c r="P62" s="31">
+      <c r="P62" s="33">
         <v>0.83</v>
       </c>
-      <c r="Q62" s="31">
+      <c r="Q62" s="33">
         <v>0.89</v>
       </c>
-      <c r="R62" s="31">
+      <c r="R62" s="33">
         <v>0.9</v>
       </c>
-      <c r="S62" s="31">
+      <c r="S62" s="33">
         <v>0.89</v>
       </c>
-      <c r="T62" s="31">
+      <c r="T62" s="33">
         <v>1.3</v>
       </c>
-      <c r="U62" s="31">
+      <c r="U62" s="33">
         <v>1.25</v>
       </c>
-      <c r="V62" s="31">
+      <c r="V62" s="33">
         <v>0.9</v>
       </c>
-      <c r="W62" s="31">
+      <c r="W62" s="33">
         <v>0.59</v>
       </c>
-      <c r="X62" s="31">
+      <c r="X62" s="33">
         <v>0.38</v>
       </c>
-      <c r="Y62" s="31">
+      <c r="Y62" s="33">
         <v>0.46</v>
       </c>
-      <c r="Z62" s="31">
+      <c r="Z62" s="33">
         <v>0.56</v>
       </c>
-      <c r="AA62" s="31">
+      <c r="AA62" s="33">
         <v>0.36</v>
       </c>
-      <c r="AB62" s="31">
+      <c r="AB62" s="33">
         <v>0.39</v>
       </c>
-      <c r="AC62" s="31">
+      <c r="AC62" s="33">
         <v>0.63</v>
       </c>
     </row>
     <row r="63" ht="15.0" customHeight="1">
-      <c r="A63" s="29" t="s">
-        <v>390</v>
-      </c>
-      <c r="B63" s="31">
+      <c r="A63" s="31" t="s">
+        <v>391</v>
+      </c>
+      <c r="B63" s="33">
         <v>1.39</v>
       </c>
-      <c r="C63" s="31">
+      <c r="C63" s="33">
         <v>1.51</v>
       </c>
-      <c r="D63" s="31">
+      <c r="D63" s="33">
         <v>1.57</v>
       </c>
-      <c r="E63" s="31">
+      <c r="E63" s="33">
         <v>1.77</v>
       </c>
-      <c r="F63" s="31">
+      <c r="F63" s="33">
         <v>1.97</v>
       </c>
-      <c r="G63" s="31">
+      <c r="G63" s="33">
         <v>2.13</v>
       </c>
-      <c r="H63" s="31">
+      <c r="H63" s="33">
         <v>2.02</v>
       </c>
-      <c r="I63" s="31">
+      <c r="I63" s="33">
         <v>1.9</v>
       </c>
-      <c r="J63" s="31">
+      <c r="J63" s="33">
         <v>1.73</v>
       </c>
-      <c r="K63" s="31">
+      <c r="K63" s="33">
         <v>1.53</v>
       </c>
-      <c r="L63" s="31">
+      <c r="L63" s="33">
         <v>1.07</v>
       </c>
-      <c r="M63" s="31">
+      <c r="M63" s="33">
         <v>0.99</v>
       </c>
-      <c r="N63" s="31">
+      <c r="N63" s="33">
         <v>0.91</v>
       </c>
-      <c r="O63" s="31">
+      <c r="O63" s="33">
         <v>0.87</v>
       </c>
-      <c r="P63" s="31">
+      <c r="P63" s="33">
         <v>0.97</v>
       </c>
-      <c r="Q63" s="31">
+      <c r="Q63" s="33">
         <v>1.06</v>
       </c>
-      <c r="R63" s="31">
+      <c r="R63" s="33">
         <v>1.06</v>
       </c>
-      <c r="S63" s="31">
+      <c r="S63" s="33">
         <v>1.01</v>
       </c>
-      <c r="T63" s="31">
+      <c r="T63" s="33">
         <v>0.94</v>
       </c>
-      <c r="U63" s="31">
+      <c r="U63" s="33">
         <v>0.75</v>
       </c>
-      <c r="V63" s="31">
+      <c r="V63" s="33">
         <v>0.59</v>
       </c>
-      <c r="W63" s="31">
+      <c r="W63" s="33">
         <v>0.47</v>
       </c>
-      <c r="X63" s="31">
+      <c r="X63" s="33">
         <v>0.43</v>
       </c>
-      <c r="Y63" s="31">
+      <c r="Y63" s="33">
         <v>0.48</v>
       </c>
-      <c r="Z63" s="32"/>
-      <c r="AA63" s="32"/>
-      <c r="AB63" s="32"/>
-      <c r="AC63" s="32"/>
+      <c r="Z63" s="34"/>
+      <c r="AA63" s="34"/>
+      <c r="AB63" s="34"/>
+      <c r="AC63" s="34"/>
     </row>
     <row r="64" ht="15.0" customHeight="1">
-      <c r="A64" s="27" t="s">
-        <v>391</v>
-      </c>
-      <c r="B64" s="28"/>
-      <c r="C64" s="28"/>
-      <c r="D64" s="28"/>
-      <c r="E64" s="28"/>
-      <c r="F64" s="28"/>
-      <c r="G64" s="28"/>
-      <c r="H64" s="28"/>
-      <c r="I64" s="28"/>
-      <c r="J64" s="28"/>
-      <c r="K64" s="28"/>
-      <c r="L64" s="28"/>
-      <c r="M64" s="28"/>
-      <c r="N64" s="28"/>
-      <c r="O64" s="28"/>
-      <c r="P64" s="28"/>
-      <c r="Q64" s="28"/>
-      <c r="R64" s="28"/>
-      <c r="S64" s="28"/>
-      <c r="T64" s="28"/>
-      <c r="U64" s="28"/>
-      <c r="V64" s="28"/>
-      <c r="W64" s="28"/>
-      <c r="X64" s="28"/>
-      <c r="Y64" s="28"/>
-      <c r="Z64" s="28"/>
-      <c r="AA64" s="28"/>
-      <c r="AB64" s="28"/>
-      <c r="AC64" s="28"/>
+      <c r="A64" s="29" t="s">
+        <v>392</v>
+      </c>
+      <c r="B64" s="30"/>
+      <c r="C64" s="30"/>
+      <c r="D64" s="30"/>
+      <c r="E64" s="30"/>
+      <c r="F64" s="30"/>
+      <c r="G64" s="30"/>
+      <c r="H64" s="30"/>
+      <c r="I64" s="30"/>
+      <c r="J64" s="30"/>
+      <c r="K64" s="30"/>
+      <c r="L64" s="30"/>
+      <c r="M64" s="30"/>
+      <c r="N64" s="30"/>
+      <c r="O64" s="30"/>
+      <c r="P64" s="30"/>
+      <c r="Q64" s="30"/>
+      <c r="R64" s="30"/>
+      <c r="S64" s="30"/>
+      <c r="T64" s="30"/>
+      <c r="U64" s="30"/>
+      <c r="V64" s="30"/>
+      <c r="W64" s="30"/>
+      <c r="X64" s="30"/>
+      <c r="Y64" s="30"/>
+      <c r="Z64" s="30"/>
+      <c r="AA64" s="30"/>
+      <c r="AB64" s="30"/>
+      <c r="AC64" s="30"/>
     </row>
     <row r="65" ht="15.0" customHeight="1">
-      <c r="A65" s="29" t="s">
-        <v>392</v>
-      </c>
-      <c r="B65" s="31">
+      <c r="A65" s="31" t="s">
+        <v>393</v>
+      </c>
+      <c r="B65" s="33">
         <v>9.14</v>
       </c>
-      <c r="C65" s="31">
+      <c r="C65" s="33">
         <v>12.48</v>
       </c>
-      <c r="D65" s="31">
+      <c r="D65" s="33">
         <v>14.91</v>
       </c>
-      <c r="E65" s="31">
+      <c r="E65" s="33">
         <v>11.87</v>
       </c>
-      <c r="F65" s="31">
+      <c r="F65" s="33">
         <v>13.96</v>
       </c>
-      <c r="G65" s="31">
+      <c r="G65" s="33">
         <v>18.73</v>
       </c>
-      <c r="H65" s="31">
+      <c r="H65" s="33">
         <v>17.07</v>
       </c>
-      <c r="I65" s="31">
+      <c r="I65" s="33">
         <v>17.01</v>
       </c>
-      <c r="J65" s="31">
+      <c r="J65" s="33">
         <v>16.54</v>
       </c>
-      <c r="K65" s="31">
+      <c r="K65" s="33">
         <v>22.62</v>
       </c>
-      <c r="L65" s="31">
+      <c r="L65" s="33">
         <v>11.5</v>
       </c>
-      <c r="M65" s="31">
+      <c r="M65" s="33">
         <v>11.31</v>
       </c>
-      <c r="N65" s="31">
+      <c r="N65" s="33">
         <v>9.45</v>
       </c>
-      <c r="O65" s="31">
+      <c r="O65" s="33">
         <v>7.67</v>
       </c>
-      <c r="P65" s="31">
+      <c r="P65" s="33">
         <v>8.27</v>
       </c>
-      <c r="Q65" s="31">
+      <c r="Q65" s="33">
         <v>13.47</v>
       </c>
-      <c r="R65" s="31">
+      <c r="R65" s="33">
         <v>17.71</v>
       </c>
-      <c r="S65" s="31">
+      <c r="S65" s="33">
         <v>8.86</v>
       </c>
-      <c r="T65" s="31">
+      <c r="T65" s="33">
         <v>12.56</v>
       </c>
-      <c r="U65" s="31">
+      <c r="U65" s="33">
         <v>11.11</v>
       </c>
-      <c r="V65" s="31">
+      <c r="V65" s="33">
         <v>7.73</v>
       </c>
-      <c r="W65" s="31">
+      <c r="W65" s="33">
         <v>5.17</v>
       </c>
-      <c r="X65" s="31">
+      <c r="X65" s="33">
         <v>3.18</v>
       </c>
-      <c r="Y65" s="31">
+      <c r="Y65" s="33">
         <v>4.05</v>
       </c>
-      <c r="Z65" s="31">
+      <c r="Z65" s="33">
         <v>4.12</v>
       </c>
-      <c r="AA65" s="31">
+      <c r="AA65" s="33">
         <v>2.72</v>
       </c>
-      <c r="AB65" s="31">
+      <c r="AB65" s="33">
         <v>4.44</v>
       </c>
-      <c r="AC65" s="31">
+      <c r="AC65" s="33">
         <v>4.66</v>
       </c>
     </row>
     <row r="66" ht="15.0" customHeight="1">
-      <c r="A66" s="29" t="s">
-        <v>393</v>
-      </c>
-      <c r="B66" s="31">
+      <c r="A66" s="31" t="s">
+        <v>394</v>
+      </c>
+      <c r="B66" s="33">
         <v>12.38</v>
       </c>
-      <c r="C66" s="31">
+      <c r="C66" s="33">
         <v>14.24</v>
       </c>
-      <c r="D66" s="31">
+      <c r="D66" s="33">
         <v>15.07</v>
       </c>
-      <c r="E66" s="31">
+      <c r="E66" s="33">
         <v>15.4</v>
       </c>
-      <c r="F66" s="31">
+      <c r="F66" s="33">
         <v>16.52</v>
       </c>
-      <c r="G66" s="31">
+      <c r="G66" s="33">
         <v>18.13</v>
       </c>
-      <c r="H66" s="31">
+      <c r="H66" s="33">
         <v>17.17</v>
       </c>
-      <c r="I66" s="31">
+      <c r="I66" s="33">
         <v>16.43</v>
       </c>
-      <c r="J66" s="31">
+      <c r="J66" s="33">
         <v>15.21</v>
       </c>
-      <c r="K66" s="31">
+      <c r="K66" s="33">
         <v>13.56</v>
       </c>
-      <c r="L66" s="31">
+      <c r="L66" s="33">
         <v>9.82</v>
       </c>
-      <c r="M66" s="31">
+      <c r="M66" s="33">
         <v>9.77</v>
       </c>
-      <c r="N66" s="31">
+      <c r="N66" s="33">
         <v>10.08</v>
       </c>
-      <c r="O66" s="31">
+      <c r="O66" s="33">
         <v>9.93</v>
       </c>
-      <c r="P66" s="31">
+      <c r="P66" s="33">
         <v>11.23</v>
       </c>
-      <c r="Q66" s="31">
+      <c r="Q66" s="33">
         <v>11.86</v>
       </c>
-      <c r="R66" s="31">
+      <c r="R66" s="33">
         <v>10.79</v>
       </c>
-      <c r="S66" s="31">
+      <c r="S66" s="33">
         <v>9.33</v>
       </c>
-      <c r="T66" s="31">
+      <c r="T66" s="33">
         <v>8.35</v>
       </c>
-      <c r="U66" s="31">
+      <c r="U66" s="33">
         <v>6.52</v>
       </c>
-      <c r="V66" s="31">
+      <c r="V66" s="33">
         <v>4.9</v>
       </c>
-      <c r="W66" s="31">
+      <c r="W66" s="33">
         <v>3.83</v>
       </c>
-      <c r="X66" s="31">
+      <c r="X66" s="33">
         <v>3.65</v>
       </c>
-      <c r="Y66" s="31">
+      <c r="Y66" s="33">
         <v>3.92</v>
       </c>
-      <c r="Z66" s="32"/>
-      <c r="AA66" s="32"/>
-      <c r="AB66" s="32"/>
-      <c r="AC66" s="32"/>
+      <c r="Z66" s="34"/>
+      <c r="AA66" s="34"/>
+      <c r="AB66" s="34"/>
+      <c r="AC66" s="34"/>
     </row>
     <row r="67" ht="15.0" customHeight="1">
-      <c r="A67" s="27" t="s">
-        <v>394</v>
-      </c>
-      <c r="B67" s="28"/>
-      <c r="C67" s="28"/>
-      <c r="D67" s="28"/>
-      <c r="E67" s="28"/>
-      <c r="F67" s="28"/>
-      <c r="G67" s="28"/>
-      <c r="H67" s="28"/>
-      <c r="I67" s="28"/>
-      <c r="J67" s="28"/>
-      <c r="K67" s="28"/>
-      <c r="L67" s="28"/>
-      <c r="M67" s="28"/>
-      <c r="N67" s="28"/>
-      <c r="O67" s="28"/>
-      <c r="P67" s="28"/>
-      <c r="Q67" s="28"/>
-      <c r="R67" s="28"/>
-      <c r="S67" s="28"/>
-      <c r="T67" s="28"/>
-      <c r="U67" s="28"/>
-      <c r="V67" s="28"/>
-      <c r="W67" s="28"/>
-      <c r="X67" s="28"/>
-      <c r="Y67" s="28"/>
-      <c r="Z67" s="28"/>
-      <c r="AA67" s="28"/>
-      <c r="AB67" s="28"/>
-      <c r="AC67" s="28"/>
+      <c r="A67" s="29" t="s">
+        <v>395</v>
+      </c>
+      <c r="B67" s="30"/>
+      <c r="C67" s="30"/>
+      <c r="D67" s="30"/>
+      <c r="E67" s="30"/>
+      <c r="F67" s="30"/>
+      <c r="G67" s="30"/>
+      <c r="H67" s="30"/>
+      <c r="I67" s="30"/>
+      <c r="J67" s="30"/>
+      <c r="K67" s="30"/>
+      <c r="L67" s="30"/>
+      <c r="M67" s="30"/>
+      <c r="N67" s="30"/>
+      <c r="O67" s="30"/>
+      <c r="P67" s="30"/>
+      <c r="Q67" s="30"/>
+      <c r="R67" s="30"/>
+      <c r="S67" s="30"/>
+      <c r="T67" s="30"/>
+      <c r="U67" s="30"/>
+      <c r="V67" s="30"/>
+      <c r="W67" s="30"/>
+      <c r="X67" s="30"/>
+      <c r="Y67" s="30"/>
+      <c r="Z67" s="30"/>
+      <c r="AA67" s="30"/>
+      <c r="AB67" s="30"/>
+      <c r="AC67" s="30"/>
     </row>
     <row r="68" ht="15.0" customHeight="1">
-      <c r="A68" s="29" t="s">
-        <v>395</v>
-      </c>
-      <c r="B68" s="31">
+      <c r="A68" s="31" t="s">
+        <v>396</v>
+      </c>
+      <c r="B68" s="33">
         <v>5.64</v>
       </c>
-      <c r="C68" s="31">
+      <c r="C68" s="33">
         <v>17.0</v>
       </c>
-      <c r="D68" s="31">
+      <c r="D68" s="33">
         <v>35.45</v>
       </c>
-      <c r="E68" s="30">
+      <c r="E68" s="32">
         <v>141.03</v>
       </c>
-      <c r="F68" s="31">
+      <c r="F68" s="33">
         <v>36.47</v>
       </c>
-      <c r="G68" s="31">
+      <c r="G68" s="33">
         <v>26.59</v>
       </c>
-      <c r="H68" s="31">
+      <c r="H68" s="33">
         <v>33.85</v>
       </c>
-      <c r="I68" s="31">
+      <c r="I68" s="33">
         <v>30.01</v>
       </c>
-      <c r="J68" s="31">
+      <c r="J68" s="33">
         <v>36.63</v>
       </c>
-      <c r="K68" s="31">
+      <c r="K68" s="33">
         <v>31.97</v>
       </c>
-      <c r="L68" s="31">
+      <c r="L68" s="33">
         <v>22.51</v>
       </c>
-      <c r="M68" s="31">
+      <c r="M68" s="33">
         <v>15.09</v>
       </c>
-      <c r="N68" s="31">
+      <c r="N68" s="33">
         <v>19.04</v>
       </c>
-      <c r="O68" s="31">
+      <c r="O68" s="33">
         <v>7.53</v>
       </c>
-      <c r="P68" s="31">
+      <c r="P68" s="33">
         <v>7.57</v>
       </c>
-      <c r="Q68" s="32"/>
-      <c r="R68" s="31">
+      <c r="Q68" s="34"/>
+      <c r="R68" s="33">
         <v>9.94</v>
       </c>
-      <c r="S68" s="31">
+      <c r="S68" s="33">
         <v>10.62</v>
       </c>
-      <c r="T68" s="31">
+      <c r="T68" s="33">
         <v>23.6</v>
       </c>
-      <c r="U68" s="31">
+      <c r="U68" s="33">
         <v>22.23</v>
       </c>
-      <c r="V68" s="31">
+      <c r="V68" s="33">
         <v>10.22</v>
       </c>
-      <c r="W68" s="31">
+      <c r="W68" s="33">
         <v>7.53</v>
       </c>
-      <c r="X68" s="31">
+      <c r="X68" s="33">
         <v>3.98</v>
       </c>
-      <c r="Y68" s="31">
+      <c r="Y68" s="33">
         <v>3.18</v>
       </c>
-      <c r="Z68" s="31">
+      <c r="Z68" s="33">
         <v>6.46</v>
       </c>
-      <c r="AA68" s="31">
+      <c r="AA68" s="33">
         <v>3.94</v>
       </c>
-      <c r="AB68" s="31">
+      <c r="AB68" s="33">
         <v>17.55</v>
       </c>
-      <c r="AC68" s="31">
+      <c r="AC68" s="33">
         <v>6.33</v>
       </c>
     </row>
     <row r="69" ht="15.0" customHeight="1">
-      <c r="A69" s="29" t="s">
-        <v>396</v>
-      </c>
-      <c r="B69" s="31">
+      <c r="A69" s="31" t="s">
+        <v>397</v>
+      </c>
+      <c r="B69" s="33">
         <v>20.13</v>
       </c>
-      <c r="C69" s="31">
+      <c r="C69" s="33">
         <v>32.96</v>
       </c>
-      <c r="D69" s="31">
+      <c r="D69" s="33">
         <v>37.85</v>
       </c>
-      <c r="E69" s="31">
+      <c r="E69" s="33">
         <v>36.53</v>
       </c>
-      <c r="F69" s="31">
+      <c r="F69" s="33">
         <v>31.93</v>
       </c>
-      <c r="G69" s="31">
+      <c r="G69" s="33">
         <v>31.05</v>
       </c>
-      <c r="H69" s="31">
+      <c r="H69" s="33">
         <v>31.67</v>
       </c>
-      <c r="I69" s="31">
+      <c r="I69" s="33">
         <v>28.18</v>
       </c>
-      <c r="J69" s="31">
+      <c r="J69" s="33">
         <v>26.39</v>
       </c>
-      <c r="K69" s="31">
+      <c r="K69" s="33">
         <v>19.7</v>
       </c>
-      <c r="L69" s="31">
+      <c r="L69" s="33">
         <v>13.12</v>
       </c>
-      <c r="M69" s="31">
+      <c r="M69" s="33">
         <v>14.73</v>
       </c>
-      <c r="N69" s="31">
+      <c r="N69" s="33">
         <v>13.51</v>
       </c>
-      <c r="O69" s="31">
+      <c r="O69" s="33">
         <v>11.82</v>
       </c>
-      <c r="P69" s="31">
+      <c r="P69" s="33">
         <v>15.81</v>
       </c>
-      <c r="Q69" s="31">
+      <c r="Q69" s="33">
         <v>20.74</v>
       </c>
-      <c r="R69" s="31">
+      <c r="R69" s="33">
         <v>14.36</v>
       </c>
-      <c r="S69" s="31">
+      <c r="S69" s="33">
         <v>14.16</v>
       </c>
-      <c r="T69" s="31">
+      <c r="T69" s="33">
         <v>12.97</v>
       </c>
-      <c r="U69" s="31">
+      <c r="U69" s="33">
         <v>8.26</v>
       </c>
-      <c r="V69" s="31">
+      <c r="V69" s="33">
         <v>5.97</v>
       </c>
-      <c r="W69" s="31">
+      <c r="W69" s="33">
         <v>4.75</v>
       </c>
-      <c r="X69" s="31">
+      <c r="X69" s="33">
         <v>4.79</v>
       </c>
-      <c r="Y69" s="31">
+      <c r="Y69" s="33">
         <v>5.24</v>
       </c>
-      <c r="Z69" s="32"/>
-      <c r="AA69" s="32"/>
-      <c r="AB69" s="32"/>
-      <c r="AC69" s="32"/>
+      <c r="Z69" s="34"/>
+      <c r="AA69" s="34"/>
+      <c r="AB69" s="34"/>
+      <c r="AC69" s="34"/>
     </row>
     <row r="70" ht="15.0" customHeight="1">
-      <c r="A70" s="27" t="s">
-        <v>397</v>
-      </c>
-      <c r="B70" s="28"/>
-      <c r="C70" s="28"/>
-      <c r="D70" s="28"/>
-      <c r="E70" s="28"/>
-      <c r="F70" s="28"/>
-      <c r="G70" s="28"/>
-      <c r="H70" s="28"/>
-      <c r="I70" s="28"/>
-      <c r="J70" s="28"/>
-      <c r="K70" s="28"/>
-      <c r="L70" s="28"/>
-      <c r="M70" s="28"/>
-      <c r="N70" s="28"/>
-      <c r="O70" s="28"/>
-      <c r="P70" s="28"/>
-      <c r="Q70" s="28"/>
-      <c r="R70" s="28"/>
-      <c r="S70" s="28"/>
-      <c r="T70" s="28"/>
-      <c r="U70" s="28"/>
-      <c r="V70" s="28"/>
-      <c r="W70" s="28"/>
-      <c r="X70" s="28"/>
-      <c r="Y70" s="28"/>
-      <c r="Z70" s="28"/>
-      <c r="AA70" s="28"/>
-      <c r="AB70" s="28"/>
-      <c r="AC70" s="28"/>
+      <c r="A70" s="29" t="s">
+        <v>398</v>
+      </c>
+      <c r="B70" s="30"/>
+      <c r="C70" s="30"/>
+      <c r="D70" s="30"/>
+      <c r="E70" s="30"/>
+      <c r="F70" s="30"/>
+      <c r="G70" s="30"/>
+      <c r="H70" s="30"/>
+      <c r="I70" s="30"/>
+      <c r="J70" s="30"/>
+      <c r="K70" s="30"/>
+      <c r="L70" s="30"/>
+      <c r="M70" s="30"/>
+      <c r="N70" s="30"/>
+      <c r="O70" s="30"/>
+      <c r="P70" s="30"/>
+      <c r="Q70" s="30"/>
+      <c r="R70" s="30"/>
+      <c r="S70" s="30"/>
+      <c r="T70" s="30"/>
+      <c r="U70" s="30"/>
+      <c r="V70" s="30"/>
+      <c r="W70" s="30"/>
+      <c r="X70" s="30"/>
+      <c r="Y70" s="30"/>
+      <c r="Z70" s="30"/>
+      <c r="AA70" s="30"/>
+      <c r="AB70" s="30"/>
+      <c r="AC70" s="30"/>
     </row>
     <row r="71" ht="15.0" customHeight="1">
-      <c r="A71" s="29" t="s">
-        <v>398</v>
-      </c>
-      <c r="B71" s="31">
+      <c r="A71" s="31" t="s">
+        <v>399</v>
+      </c>
+      <c r="B71" s="33">
         <v>6.45</v>
       </c>
-      <c r="C71" s="31">
+      <c r="C71" s="33">
         <v>33.17</v>
       </c>
-      <c r="D71" s="32"/>
-      <c r="E71" s="32"/>
-      <c r="F71" s="30">
+      <c r="D71" s="34"/>
+      <c r="E71" s="34"/>
+      <c r="F71" s="32">
         <v>714.05</v>
       </c>
-      <c r="G71" s="31">
+      <c r="G71" s="33">
         <v>55.77</v>
       </c>
-      <c r="H71" s="30">
+      <c r="H71" s="32">
         <v>179.25</v>
       </c>
-      <c r="I71" s="31">
+      <c r="I71" s="33">
         <v>96.48</v>
       </c>
-      <c r="J71" s="30">
+      <c r="J71" s="32">
         <v>202.05</v>
       </c>
-      <c r="K71" s="31">
+      <c r="K71" s="33">
         <v>45.38</v>
       </c>
-      <c r="L71" s="32"/>
-      <c r="M71" s="31">
+      <c r="L71" s="34"/>
+      <c r="M71" s="33">
         <v>62.95</v>
       </c>
-      <c r="N71" s="31">
+      <c r="N71" s="33">
         <v>41.88</v>
       </c>
-      <c r="O71" s="31">
+      <c r="O71" s="33">
         <v>9.69</v>
       </c>
-      <c r="P71" s="31">
+      <c r="P71" s="33">
         <v>10.34</v>
       </c>
-      <c r="Q71" s="32"/>
-      <c r="R71" s="32"/>
-      <c r="S71" s="32"/>
-      <c r="T71" s="31">
+      <c r="Q71" s="34"/>
+      <c r="R71" s="34"/>
+      <c r="S71" s="34"/>
+      <c r="T71" s="33">
         <v>68.04</v>
       </c>
-      <c r="U71" s="31">
+      <c r="U71" s="33">
         <v>48.76</v>
       </c>
-      <c r="V71" s="31">
+      <c r="V71" s="33">
         <v>12.08</v>
       </c>
-      <c r="W71" s="31">
+      <c r="W71" s="33">
         <v>12.35</v>
       </c>
-      <c r="X71" s="31">
+      <c r="X71" s="33">
         <v>4.23</v>
       </c>
-      <c r="Y71" s="31">
+      <c r="Y71" s="33">
         <v>3.75</v>
       </c>
-      <c r="Z71" s="31">
+      <c r="Z71" s="33">
         <v>18.12</v>
       </c>
-      <c r="AA71" s="31">
+      <c r="AA71" s="33">
         <v>5.94</v>
       </c>
-      <c r="AB71" s="32"/>
-      <c r="AC71" s="31">
+      <c r="AB71" s="34"/>
+      <c r="AC71" s="33">
         <v>38.93</v>
       </c>
     </row>
     <row r="72" ht="15.0" customHeight="1">
-      <c r="A72" s="29" t="s">
-        <v>399</v>
-      </c>
-      <c r="B72" s="31">
+      <c r="A72" s="31" t="s">
+        <v>400</v>
+      </c>
+      <c r="B72" s="33">
         <v>52.46</v>
       </c>
-      <c r="C72" s="30">
+      <c r="C72" s="32">
         <v>699.29</v>
       </c>
-      <c r="D72" s="32"/>
-      <c r="E72" s="30">
+      <c r="D72" s="34"/>
+      <c r="E72" s="32">
         <v>429.54</v>
       </c>
-      <c r="F72" s="30">
+      <c r="F72" s="32">
         <v>120.36</v>
       </c>
-      <c r="G72" s="31">
+      <c r="G72" s="33">
         <v>81.55</v>
       </c>
-      <c r="H72" s="30">
+      <c r="H72" s="32">
         <v>118.43</v>
       </c>
-      <c r="I72" s="31">
+      <c r="I72" s="33">
         <v>98.16</v>
       </c>
-      <c r="J72" s="31">
+      <c r="J72" s="33">
         <v>88.01</v>
       </c>
-      <c r="K72" s="31">
+      <c r="K72" s="33">
         <v>44.93</v>
       </c>
-      <c r="L72" s="31">
+      <c r="L72" s="33">
         <v>30.6</v>
       </c>
-      <c r="M72" s="31">
+      <c r="M72" s="33">
         <v>41.47</v>
       </c>
-      <c r="N72" s="31">
+      <c r="N72" s="33">
         <v>64.31</v>
       </c>
-      <c r="O72" s="32"/>
-      <c r="P72" s="32"/>
-      <c r="Q72" s="32"/>
-      <c r="R72" s="30">
+      <c r="O72" s="34"/>
+      <c r="P72" s="34"/>
+      <c r="Q72" s="34"/>
+      <c r="R72" s="32">
         <v>140.45</v>
       </c>
-      <c r="S72" s="31">
+      <c r="S72" s="33">
         <v>47.23</v>
       </c>
-      <c r="T72" s="31">
+      <c r="T72" s="33">
         <v>19.59</v>
       </c>
-      <c r="U72" s="31">
+      <c r="U72" s="33">
         <v>10.72</v>
       </c>
-      <c r="V72" s="31">
+      <c r="V72" s="33">
         <v>8.08</v>
       </c>
-      <c r="W72" s="31">
+      <c r="W72" s="33">
         <v>6.74</v>
       </c>
-      <c r="X72" s="31">
+      <c r="X72" s="33">
         <v>8.23</v>
       </c>
-      <c r="Y72" s="31">
+      <c r="Y72" s="33">
         <v>12.2</v>
       </c>
-      <c r="Z72" s="32"/>
-      <c r="AA72" s="32"/>
-      <c r="AB72" s="32"/>
-      <c r="AC72" s="32"/>
+      <c r="Z72" s="34"/>
+      <c r="AA72" s="34"/>
+      <c r="AB72" s="34"/>
+      <c r="AC72" s="34"/>
     </row>
     <row r="73" ht="15.75" customHeight="1"/>
     <row r="74" ht="15.75" customHeight="1"/>
